--- a/build/templates/Resumen_1ro_2do.xlsx
+++ b/build/templates/Resumen_1ro_2do.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JavierWorkSpace\BatallaProject\backend\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1D8ED3-0FA1-4843-A81D-09DD61DB05A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C8EAA7-B760-4030-85ED-9EAD7B6CCC01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{299BAFB4-AE58-4015-B36E-D7CD92F1B4DD}"/>
   </bookViews>
@@ -2230,467 +2230,8 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -2742,6 +2283,465 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="69" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="62" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2765,22 +2765,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>43908</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>9861</xdr:rowOff>
+      <xdr:colOff>32845</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>55842</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>953886</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>180639</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>373664</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>26274</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 2">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E2AB10B-FCE1-4A32-92D5-5B1ABD0EC41F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABBDD501-D84A-4BA3-8E12-3BDFC35BC22B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2789,20 +2789,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="43908" y="134100"/>
-          <a:ext cx="4604021" cy="692582"/>
+          <a:off x="32845" y="55842"/>
+          <a:ext cx="3465019" cy="818157"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3133,116 +3128,116 @@
   <sheetData>
     <row r="1" spans="1:28" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H1" s="9"/>
-      <c r="N1" s="45" t="s">
+      <c r="N1" s="174" t="s">
         <v>98</v>
       </c>
-      <c r="O1" s="45"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="45"/>
-      <c r="R1" s="45"/>
-      <c r="S1" s="45"/>
-      <c r="T1" s="45"/>
-      <c r="U1" s="45"/>
-      <c r="V1" s="45"/>
-      <c r="W1" s="45"/>
-      <c r="X1" s="45"/>
-      <c r="Y1" s="45"/>
+      <c r="O1" s="174"/>
+      <c r="P1" s="174"/>
+      <c r="Q1" s="174"/>
+      <c r="R1" s="174"/>
+      <c r="S1" s="174"/>
+      <c r="T1" s="174"/>
+      <c r="U1" s="174"/>
+      <c r="V1" s="174"/>
+      <c r="W1" s="174"/>
+      <c r="X1" s="174"/>
+      <c r="Y1" s="174"/>
     </row>
     <row r="2" spans="1:28" s="8" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46"/>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="N2" s="47" t="s">
+      <c r="A2" s="221"/>
+      <c r="B2" s="221"/>
+      <c r="C2" s="221"/>
+      <c r="D2" s="221"/>
+      <c r="E2" s="221"/>
+      <c r="F2" s="221"/>
+      <c r="G2" s="221"/>
+      <c r="H2" s="221"/>
+      <c r="N2" s="141" t="s">
         <v>97</v>
       </c>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="47"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="47"/>
-      <c r="T2" s="47"/>
-      <c r="U2" s="47"/>
-      <c r="V2" s="47"/>
-      <c r="W2" s="47"/>
-      <c r="X2" s="47"/>
-      <c r="Y2" s="47"/>
+      <c r="O2" s="141"/>
+      <c r="P2" s="141"/>
+      <c r="Q2" s="141"/>
+      <c r="R2" s="141"/>
+      <c r="S2" s="141"/>
+      <c r="T2" s="141"/>
+      <c r="U2" s="141"/>
+      <c r="V2" s="141"/>
+      <c r="W2" s="141"/>
+      <c r="X2" s="141"/>
+      <c r="Y2" s="141"/>
     </row>
     <row r="3" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="48" t="s">
+      <c r="A3" s="221"/>
+      <c r="B3" s="221"/>
+      <c r="C3" s="221"/>
+      <c r="D3" s="221"/>
+      <c r="E3" s="221"/>
+      <c r="F3" s="221"/>
+      <c r="G3" s="221"/>
+      <c r="H3" s="221"/>
+      <c r="I3" s="222" t="s">
         <v>94</v>
       </c>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="49"/>
-      <c r="O3" s="49"/>
-      <c r="P3" s="49"/>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="49"/>
-      <c r="S3" s="49"/>
-      <c r="T3" s="49"/>
-      <c r="U3" s="49"/>
-      <c r="V3" s="49"/>
-      <c r="W3" s="49"/>
-      <c r="X3" s="49"/>
-      <c r="Y3" s="49"/>
-      <c r="Z3" s="49"/>
+      <c r="J3" s="222"/>
+      <c r="K3" s="222"/>
+      <c r="L3" s="222"/>
+      <c r="M3" s="187"/>
+      <c r="N3" s="187"/>
+      <c r="O3" s="187"/>
+      <c r="P3" s="187"/>
+      <c r="Q3" s="187"/>
+      <c r="R3" s="187"/>
+      <c r="S3" s="187"/>
+      <c r="T3" s="187"/>
+      <c r="U3" s="187"/>
+      <c r="V3" s="187"/>
+      <c r="W3" s="187"/>
+      <c r="X3" s="187"/>
+      <c r="Y3" s="187"/>
+      <c r="Z3" s="187"/>
     </row>
     <row r="4" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="48" t="s">
+      <c r="A4" s="221"/>
+      <c r="B4" s="221"/>
+      <c r="C4" s="221"/>
+      <c r="D4" s="221"/>
+      <c r="E4" s="221"/>
+      <c r="F4" s="221"/>
+      <c r="G4" s="221"/>
+      <c r="H4" s="221"/>
+      <c r="I4" s="222" t="s">
         <v>95</v>
       </c>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="48"/>
-      <c r="M4" s="48"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="51"/>
-      <c r="P4" s="51"/>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="51"/>
-      <c r="S4" s="51"/>
-      <c r="T4" s="51"/>
-      <c r="U4" s="51"/>
-      <c r="V4" s="51"/>
-      <c r="W4" s="50" t="s">
+      <c r="J4" s="222"/>
+      <c r="K4" s="222"/>
+      <c r="L4" s="222"/>
+      <c r="M4" s="222"/>
+      <c r="N4" s="224"/>
+      <c r="O4" s="224"/>
+      <c r="P4" s="224"/>
+      <c r="Q4" s="224"/>
+      <c r="R4" s="224"/>
+      <c r="S4" s="224"/>
+      <c r="T4" s="224"/>
+      <c r="U4" s="224"/>
+      <c r="V4" s="224"/>
+      <c r="W4" s="223" t="s">
         <v>96</v>
       </c>
-      <c r="X4" s="50"/>
-      <c r="Y4" s="50"/>
+      <c r="X4" s="223"/>
+      <c r="Y4" s="223"/>
       <c r="Z4" s="10"/>
     </row>
     <row r="5" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="46"/>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
+      <c r="A5" s="221"/>
+      <c r="B5" s="221"/>
+      <c r="C5" s="221"/>
+      <c r="D5" s="221"/>
+      <c r="E5" s="221"/>
+      <c r="F5" s="221"/>
+      <c r="G5" s="221"/>
+      <c r="H5" s="221"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
@@ -3263,12 +3258,12 @@
       <c r="Z5" s="5"/>
     </row>
     <row r="6" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="52" t="s">
+      <c r="A6" s="225" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
+      <c r="B6" s="225"/>
+      <c r="C6" s="225"/>
+      <c r="D6" s="225"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -3293,263 +3288,263 @@
       <c r="Z6" s="5"/>
     </row>
     <row r="7" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="53" t="s">
+      <c r="A7" s="185" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="54" t="s">
+      <c r="B7" s="185"/>
+      <c r="C7" s="185"/>
+      <c r="D7" s="185"/>
+      <c r="E7" s="187"/>
+      <c r="F7" s="187"/>
+      <c r="G7" s="187"/>
+      <c r="H7" s="219" t="s">
         <v>99</v>
       </c>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
-      <c r="K7" s="55"/>
-      <c r="L7" s="55"/>
-      <c r="M7" s="55"/>
-      <c r="N7" s="55"/>
-      <c r="O7" s="55"/>
-      <c r="P7" s="55"/>
-      <c r="Q7" s="55"/>
-      <c r="R7" s="55"/>
-      <c r="S7" s="55"/>
-      <c r="T7" s="55"/>
-      <c r="U7" s="55"/>
-      <c r="V7" s="55"/>
-      <c r="W7" s="55"/>
-      <c r="X7" s="55"/>
+      <c r="I7" s="219"/>
+      <c r="J7" s="220"/>
+      <c r="K7" s="220"/>
+      <c r="L7" s="220"/>
+      <c r="M7" s="220"/>
+      <c r="N7" s="220"/>
+      <c r="O7" s="220"/>
+      <c r="P7" s="220"/>
+      <c r="Q7" s="220"/>
+      <c r="R7" s="220"/>
+      <c r="S7" s="220"/>
+      <c r="T7" s="220"/>
+      <c r="U7" s="220"/>
+      <c r="V7" s="220"/>
+      <c r="W7" s="220"/>
+      <c r="X7" s="220"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
     <row r="8" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="185" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="53"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="49"/>
-      <c r="N8" s="49"/>
-      <c r="O8" s="49"/>
-      <c r="P8" s="49"/>
-      <c r="Q8" s="49"/>
-      <c r="R8" s="56" t="s">
+      <c r="B8" s="185"/>
+      <c r="C8" s="187"/>
+      <c r="D8" s="187"/>
+      <c r="E8" s="187"/>
+      <c r="F8" s="187"/>
+      <c r="G8" s="187"/>
+      <c r="H8" s="187"/>
+      <c r="I8" s="187"/>
+      <c r="J8" s="187"/>
+      <c r="K8" s="187"/>
+      <c r="L8" s="187"/>
+      <c r="M8" s="187"/>
+      <c r="N8" s="187"/>
+      <c r="O8" s="187"/>
+      <c r="P8" s="187"/>
+      <c r="Q8" s="187"/>
+      <c r="R8" s="186" t="s">
         <v>91</v>
       </c>
-      <c r="S8" s="56"/>
-      <c r="T8" s="56"/>
-      <c r="U8" s="49"/>
-      <c r="V8" s="49"/>
-      <c r="W8" s="49"/>
-      <c r="X8" s="49"/>
-      <c r="Y8" s="49"/>
-      <c r="Z8" s="49"/>
+      <c r="S8" s="186"/>
+      <c r="T8" s="186"/>
+      <c r="U8" s="187"/>
+      <c r="V8" s="187"/>
+      <c r="W8" s="187"/>
+      <c r="X8" s="187"/>
+      <c r="Y8" s="187"/>
+      <c r="Z8" s="187"/>
     </row>
     <row r="9" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="185" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="53"/>
-      <c r="C9" s="60"/>
-      <c r="D9" s="60"/>
-      <c r="E9" s="60"/>
+      <c r="B9" s="185"/>
+      <c r="C9" s="96"/>
+      <c r="D9" s="96"/>
+      <c r="E9" s="96"/>
       <c r="F9" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G9" s="60"/>
-      <c r="H9" s="60"/>
-      <c r="I9" s="56" t="s">
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="186" t="s">
         <v>87</v>
       </c>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="56"/>
-      <c r="M9" s="56"/>
-      <c r="N9" s="49"/>
-      <c r="O9" s="49"/>
-      <c r="P9" s="49"/>
-      <c r="Q9" s="49"/>
-      <c r="R9" s="49"/>
-      <c r="S9" s="49"/>
-      <c r="T9" s="49"/>
-      <c r="U9" s="49"/>
-      <c r="V9" s="56"/>
-      <c r="W9" s="56"/>
-      <c r="X9" s="56"/>
-      <c r="Y9" s="56"/>
-      <c r="Z9" s="56"/>
+      <c r="J9" s="186"/>
+      <c r="K9" s="186"/>
+      <c r="L9" s="186"/>
+      <c r="M9" s="186"/>
+      <c r="N9" s="187"/>
+      <c r="O9" s="187"/>
+      <c r="P9" s="187"/>
+      <c r="Q9" s="187"/>
+      <c r="R9" s="187"/>
+      <c r="S9" s="187"/>
+      <c r="T9" s="187"/>
+      <c r="U9" s="187"/>
+      <c r="V9" s="186"/>
+      <c r="W9" s="186"/>
+      <c r="X9" s="186"/>
+      <c r="Y9" s="186"/>
+      <c r="Z9" s="186"/>
     </row>
     <row r="10" spans="1:28" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="185" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="54" t="s">
+      <c r="B10" s="185"/>
+      <c r="C10" s="185"/>
+      <c r="D10" s="185"/>
+      <c r="E10" s="185"/>
+      <c r="F10" s="185"/>
+      <c r="G10" s="185"/>
+      <c r="H10" s="185"/>
+      <c r="I10" s="219" t="s">
         <v>72</v>
       </c>
-      <c r="J10" s="54"/>
-      <c r="K10" s="54"/>
-      <c r="L10" s="54"/>
-      <c r="M10" s="54"/>
-      <c r="N10" s="53"/>
-      <c r="O10" s="53"/>
-      <c r="P10" s="53"/>
-      <c r="Q10" s="53"/>
-      <c r="R10" s="53"/>
-      <c r="S10" s="53"/>
-      <c r="T10" s="53"/>
-      <c r="U10" s="53"/>
-      <c r="V10" s="53"/>
-      <c r="W10" s="53"/>
-      <c r="X10" s="53"/>
-      <c r="Y10" s="53"/>
-      <c r="Z10" s="53"/>
+      <c r="J10" s="219"/>
+      <c r="K10" s="219"/>
+      <c r="L10" s="219"/>
+      <c r="M10" s="219"/>
+      <c r="N10" s="185"/>
+      <c r="O10" s="185"/>
+      <c r="P10" s="185"/>
+      <c r="Q10" s="185"/>
+      <c r="R10" s="185"/>
+      <c r="S10" s="185"/>
+      <c r="T10" s="185"/>
+      <c r="U10" s="185"/>
+      <c r="V10" s="185"/>
+      <c r="W10" s="185"/>
+      <c r="X10" s="185"/>
+      <c r="Y10" s="185"/>
+      <c r="Z10" s="185"/>
     </row>
     <row r="11" spans="1:28" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="57" t="s">
+      <c r="A11" s="182" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="58"/>
-      <c r="L11" s="58"/>
-      <c r="M11" s="59"/>
-      <c r="N11" s="58" t="s">
+      <c r="B11" s="183"/>
+      <c r="C11" s="183"/>
+      <c r="D11" s="183"/>
+      <c r="E11" s="183"/>
+      <c r="F11" s="183"/>
+      <c r="G11" s="183"/>
+      <c r="H11" s="183"/>
+      <c r="I11" s="183"/>
+      <c r="J11" s="183"/>
+      <c r="K11" s="183"/>
+      <c r="L11" s="183"/>
+      <c r="M11" s="184"/>
+      <c r="N11" s="183" t="s">
         <v>47</v>
       </c>
-      <c r="O11" s="58"/>
-      <c r="P11" s="58"/>
-      <c r="Q11" s="58"/>
-      <c r="R11" s="58"/>
-      <c r="S11" s="58"/>
-      <c r="T11" s="58"/>
-      <c r="U11" s="58"/>
-      <c r="V11" s="58"/>
-      <c r="W11" s="58"/>
-      <c r="X11" s="58"/>
-      <c r="Y11" s="58"/>
-      <c r="Z11" s="59"/>
+      <c r="O11" s="183"/>
+      <c r="P11" s="183"/>
+      <c r="Q11" s="183"/>
+      <c r="R11" s="183"/>
+      <c r="S11" s="183"/>
+      <c r="T11" s="183"/>
+      <c r="U11" s="183"/>
+      <c r="V11" s="183"/>
+      <c r="W11" s="183"/>
+      <c r="X11" s="183"/>
+      <c r="Y11" s="183"/>
+      <c r="Z11" s="184"/>
     </row>
     <row r="12" spans="1:28" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="74" t="s">
+      <c r="A12" s="201" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="77" t="s">
+      <c r="B12" s="204" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="78"/>
-      <c r="D12" s="83" t="s">
+      <c r="C12" s="205"/>
+      <c r="D12" s="210" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="84"/>
-      <c r="F12" s="83" t="s">
+      <c r="E12" s="211"/>
+      <c r="F12" s="210" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="84"/>
-      <c r="H12" s="89" t="s">
+      <c r="G12" s="211"/>
+      <c r="H12" s="216" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="74" t="s">
+      <c r="I12" s="201" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="61" t="s">
+      <c r="J12" s="188" t="s">
         <v>41</v>
       </c>
-      <c r="K12" s="64" t="s">
+      <c r="K12" s="191" t="s">
         <v>45</v>
       </c>
-      <c r="L12" s="65"/>
-      <c r="M12" s="66"/>
-      <c r="N12" s="116" t="s">
+      <c r="L12" s="192"/>
+      <c r="M12" s="193"/>
+      <c r="N12" s="84" t="s">
         <v>49</v>
       </c>
-      <c r="O12" s="116"/>
-      <c r="P12" s="116"/>
-      <c r="Q12" s="116"/>
-      <c r="R12" s="116"/>
-      <c r="S12" s="116"/>
-      <c r="T12" s="116"/>
-      <c r="U12" s="116"/>
-      <c r="V12" s="116"/>
-      <c r="W12" s="214" t="s">
+      <c r="O12" s="84"/>
+      <c r="P12" s="84"/>
+      <c r="Q12" s="84"/>
+      <c r="R12" s="84"/>
+      <c r="S12" s="84"/>
+      <c r="T12" s="84"/>
+      <c r="U12" s="84"/>
+      <c r="V12" s="84"/>
+      <c r="W12" s="57" t="s">
         <v>50</v>
       </c>
-      <c r="X12" s="215"/>
-      <c r="Y12" s="215"/>
-      <c r="Z12" s="216"/>
-    </row>
-    <row r="13" spans="1:28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="75"/>
-      <c r="B13" s="79"/>
-      <c r="C13" s="80"/>
-      <c r="D13" s="85"/>
-      <c r="E13" s="86"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="86"/>
-      <c r="H13" s="90"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="67"/>
-      <c r="L13" s="68"/>
-      <c r="M13" s="69"/>
-      <c r="N13" s="119" t="s">
+      <c r="X12" s="58"/>
+      <c r="Y12" s="58"/>
+      <c r="Z12" s="59"/>
+    </row>
+    <row r="13" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="202"/>
+      <c r="B13" s="206"/>
+      <c r="C13" s="207"/>
+      <c r="D13" s="212"/>
+      <c r="E13" s="213"/>
+      <c r="F13" s="212"/>
+      <c r="G13" s="213"/>
+      <c r="H13" s="217"/>
+      <c r="I13" s="202"/>
+      <c r="J13" s="189"/>
+      <c r="K13" s="194"/>
+      <c r="L13" s="195"/>
+      <c r="M13" s="196"/>
+      <c r="N13" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="O13" s="119"/>
-      <c r="P13" s="119"/>
-      <c r="Q13" s="119"/>
-      <c r="R13" s="119"/>
-      <c r="S13" s="119"/>
-      <c r="T13" s="119"/>
-      <c r="U13" s="119"/>
-      <c r="V13" s="119"/>
-      <c r="W13" s="217"/>
-      <c r="X13" s="218"/>
-      <c r="Y13" s="218"/>
-      <c r="Z13" s="219"/>
+      <c r="O13" s="85"/>
+      <c r="P13" s="85"/>
+      <c r="Q13" s="85"/>
+      <c r="R13" s="85"/>
+      <c r="S13" s="85"/>
+      <c r="T13" s="85"/>
+      <c r="U13" s="85"/>
+      <c r="V13" s="85"/>
+      <c r="W13" s="60"/>
+      <c r="X13" s="61"/>
+      <c r="Y13" s="61"/>
+      <c r="Z13" s="62"/>
     </row>
     <row r="14" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="75"/>
-      <c r="B14" s="79"/>
-      <c r="C14" s="80"/>
-      <c r="D14" s="85"/>
-      <c r="E14" s="86"/>
-      <c r="F14" s="85"/>
-      <c r="G14" s="86"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="75"/>
-      <c r="J14" s="62"/>
-      <c r="K14" s="70" t="s">
+      <c r="A14" s="202"/>
+      <c r="B14" s="206"/>
+      <c r="C14" s="207"/>
+      <c r="D14" s="212"/>
+      <c r="E14" s="213"/>
+      <c r="F14" s="212"/>
+      <c r="G14" s="213"/>
+      <c r="H14" s="217"/>
+      <c r="I14" s="202"/>
+      <c r="J14" s="189"/>
+      <c r="K14" s="197" t="s">
         <v>42</v>
       </c>
-      <c r="L14" s="70" t="s">
+      <c r="L14" s="197" t="s">
         <v>43</v>
       </c>
-      <c r="M14" s="72" t="s">
+      <c r="M14" s="199" t="s">
         <v>44</v>
       </c>
       <c r="N14" s="16" t="s">
@@ -3579,25 +3574,25 @@
       <c r="V14" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="W14" s="217"/>
-      <c r="X14" s="218"/>
-      <c r="Y14" s="218"/>
-      <c r="Z14" s="219"/>
+      <c r="W14" s="60"/>
+      <c r="X14" s="61"/>
+      <c r="Y14" s="61"/>
+      <c r="Z14" s="62"/>
     </row>
     <row r="15" spans="1:28" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="76"/>
-      <c r="B15" s="81"/>
-      <c r="C15" s="82"/>
-      <c r="D15" s="87"/>
-      <c r="E15" s="88"/>
-      <c r="F15" s="87"/>
-      <c r="G15" s="88"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="76"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="71"/>
-      <c r="L15" s="71"/>
-      <c r="M15" s="73"/>
+      <c r="A15" s="203"/>
+      <c r="B15" s="208"/>
+      <c r="C15" s="209"/>
+      <c r="D15" s="214"/>
+      <c r="E15" s="215"/>
+      <c r="F15" s="214"/>
+      <c r="G15" s="215"/>
+      <c r="H15" s="218"/>
+      <c r="I15" s="203"/>
+      <c r="J15" s="190"/>
+      <c r="K15" s="198"/>
+      <c r="L15" s="198"/>
+      <c r="M15" s="200"/>
       <c r="N15" s="41" t="s">
         <v>104</v>
       </c>
@@ -3625,27 +3620,27 @@
       <c r="V15" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="W15" s="220"/>
-      <c r="X15" s="221"/>
-      <c r="Y15" s="221"/>
-      <c r="Z15" s="222"/>
+      <c r="W15" s="63"/>
+      <c r="X15" s="64"/>
+      <c r="Y15" s="64"/>
+      <c r="Z15" s="65"/>
     </row>
     <row r="16" spans="1:28" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="96" t="s">
+      <c r="B16" s="178" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="97"/>
-      <c r="D16" s="98" t="s">
+      <c r="C16" s="179"/>
+      <c r="D16" s="180" t="s">
         <v>101</v>
       </c>
-      <c r="E16" s="99"/>
-      <c r="F16" s="98" t="s">
+      <c r="E16" s="181"/>
+      <c r="F16" s="180" t="s">
         <v>102</v>
       </c>
-      <c r="G16" s="99"/>
+      <c r="G16" s="181"/>
       <c r="H16" s="34" t="s">
         <v>103</v>
       </c>
@@ -3691,30 +3686,30 @@
       <c r="V16" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="W16" s="223" t="s">
+      <c r="W16" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="X16" s="224"/>
-      <c r="Y16" s="224"/>
-      <c r="Z16" s="225"/>
+      <c r="X16" s="67"/>
+      <c r="Y16" s="67"/>
+      <c r="Z16" s="68"/>
       <c r="AB16" s="6"/>
     </row>
     <row r="17" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="92" t="s">
+      <c r="B17" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C17" s="93"/>
-      <c r="D17" s="94" t="s">
+      <c r="C17" s="177"/>
+      <c r="D17" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E17" s="95"/>
-      <c r="F17" s="94" t="s">
+      <c r="E17" s="117"/>
+      <c r="F17" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G17" s="95"/>
+      <c r="G17" s="117"/>
       <c r="H17" s="17" t="s">
         <v>103</v>
       </c>
@@ -3760,30 +3755,30 @@
       <c r="V17" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W17" s="100" t="s">
+      <c r="W17" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X17" s="101"/>
-      <c r="Y17" s="101"/>
-      <c r="Z17" s="102"/>
+      <c r="X17" s="70"/>
+      <c r="Y17" s="70"/>
+      <c r="Z17" s="71"/>
       <c r="AC17" s="7"/>
     </row>
     <row r="18" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="92" t="s">
+      <c r="B18" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="93"/>
-      <c r="D18" s="94" t="s">
+      <c r="C18" s="177"/>
+      <c r="D18" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E18" s="95"/>
-      <c r="F18" s="94" t="s">
+      <c r="E18" s="117"/>
+      <c r="F18" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G18" s="95"/>
+      <c r="G18" s="117"/>
       <c r="H18" s="17" t="s">
         <v>103</v>
       </c>
@@ -3829,29 +3824,29 @@
       <c r="V18" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W18" s="100" t="s">
+      <c r="W18" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X18" s="101"/>
-      <c r="Y18" s="101"/>
-      <c r="Z18" s="102"/>
+      <c r="X18" s="70"/>
+      <c r="Y18" s="70"/>
+      <c r="Z18" s="71"/>
     </row>
     <row r="19" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="92" t="s">
+      <c r="B19" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C19" s="93"/>
-      <c r="D19" s="94" t="s">
+      <c r="C19" s="177"/>
+      <c r="D19" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="95"/>
-      <c r="F19" s="94" t="s">
+      <c r="E19" s="117"/>
+      <c r="F19" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G19" s="95"/>
+      <c r="G19" s="117"/>
       <c r="H19" s="17" t="s">
         <v>103</v>
       </c>
@@ -3897,29 +3892,29 @@
       <c r="V19" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W19" s="100" t="s">
+      <c r="W19" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X19" s="101"/>
-      <c r="Y19" s="101"/>
-      <c r="Z19" s="102"/>
+      <c r="X19" s="70"/>
+      <c r="Y19" s="70"/>
+      <c r="Z19" s="71"/>
     </row>
     <row r="20" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="92" t="s">
+      <c r="B20" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="93"/>
-      <c r="D20" s="94" t="s">
+      <c r="C20" s="177"/>
+      <c r="D20" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="94" t="s">
+      <c r="E20" s="117"/>
+      <c r="F20" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G20" s="95"/>
+      <c r="G20" s="117"/>
       <c r="H20" s="17" t="s">
         <v>103</v>
       </c>
@@ -3965,29 +3960,29 @@
       <c r="V20" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W20" s="100" t="s">
+      <c r="W20" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X20" s="101"/>
-      <c r="Y20" s="101"/>
-      <c r="Z20" s="102"/>
+      <c r="X20" s="70"/>
+      <c r="Y20" s="70"/>
+      <c r="Z20" s="71"/>
     </row>
     <row r="21" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="92" t="s">
+      <c r="B21" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C21" s="93"/>
-      <c r="D21" s="94" t="s">
+      <c r="C21" s="177"/>
+      <c r="D21" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E21" s="95"/>
-      <c r="F21" s="94" t="s">
+      <c r="E21" s="117"/>
+      <c r="F21" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G21" s="95"/>
+      <c r="G21" s="117"/>
       <c r="H21" s="17" t="s">
         <v>103</v>
       </c>
@@ -4033,29 +4028,29 @@
       <c r="V21" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W21" s="100" t="s">
+      <c r="W21" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X21" s="101"/>
-      <c r="Y21" s="101"/>
-      <c r="Z21" s="102"/>
+      <c r="X21" s="70"/>
+      <c r="Y21" s="70"/>
+      <c r="Z21" s="71"/>
     </row>
     <row r="22" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="92" t="s">
+      <c r="B22" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C22" s="93"/>
-      <c r="D22" s="94" t="s">
+      <c r="C22" s="177"/>
+      <c r="D22" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E22" s="95"/>
-      <c r="F22" s="94" t="s">
+      <c r="E22" s="117"/>
+      <c r="F22" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G22" s="95"/>
+      <c r="G22" s="117"/>
       <c r="H22" s="17" t="s">
         <v>103</v>
       </c>
@@ -4101,29 +4096,29 @@
       <c r="V22" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W22" s="100" t="s">
+      <c r="W22" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X22" s="101"/>
-      <c r="Y22" s="101"/>
-      <c r="Z22" s="102"/>
+      <c r="X22" s="70"/>
+      <c r="Y22" s="70"/>
+      <c r="Z22" s="71"/>
     </row>
     <row r="23" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B23" s="92" t="s">
+      <c r="B23" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="93"/>
-      <c r="D23" s="94" t="s">
+      <c r="C23" s="177"/>
+      <c r="D23" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E23" s="95"/>
-      <c r="F23" s="94" t="s">
+      <c r="E23" s="117"/>
+      <c r="F23" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G23" s="95"/>
+      <c r="G23" s="117"/>
       <c r="H23" s="17" t="s">
         <v>103</v>
       </c>
@@ -4169,29 +4164,29 @@
       <c r="V23" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W23" s="100" t="s">
+      <c r="W23" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X23" s="101"/>
-      <c r="Y23" s="101"/>
-      <c r="Z23" s="102"/>
+      <c r="X23" s="70"/>
+      <c r="Y23" s="70"/>
+      <c r="Z23" s="71"/>
     </row>
     <row r="24" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="92" t="s">
+      <c r="B24" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C24" s="93"/>
-      <c r="D24" s="94" t="s">
+      <c r="C24" s="177"/>
+      <c r="D24" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E24" s="95"/>
-      <c r="F24" s="94" t="s">
+      <c r="E24" s="117"/>
+      <c r="F24" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G24" s="95"/>
+      <c r="G24" s="117"/>
       <c r="H24" s="17" t="s">
         <v>103</v>
       </c>
@@ -4237,29 +4232,29 @@
       <c r="V24" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W24" s="100" t="s">
+      <c r="W24" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X24" s="101"/>
-      <c r="Y24" s="101"/>
-      <c r="Z24" s="102"/>
+      <c r="X24" s="70"/>
+      <c r="Y24" s="70"/>
+      <c r="Z24" s="71"/>
     </row>
     <row r="25" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="92" t="s">
+      <c r="B25" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="93"/>
-      <c r="D25" s="94" t="s">
+      <c r="C25" s="177"/>
+      <c r="D25" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="95"/>
-      <c r="F25" s="94" t="s">
+      <c r="E25" s="117"/>
+      <c r="F25" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G25" s="95"/>
+      <c r="G25" s="117"/>
       <c r="H25" s="17" t="s">
         <v>103</v>
       </c>
@@ -4305,29 +4300,29 @@
       <c r="V25" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W25" s="100" t="s">
+      <c r="W25" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X25" s="101"/>
-      <c r="Y25" s="101"/>
-      <c r="Z25" s="102"/>
+      <c r="X25" s="70"/>
+      <c r="Y25" s="70"/>
+      <c r="Z25" s="71"/>
     </row>
     <row r="26" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="B26" s="92" t="s">
+      <c r="B26" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C26" s="93"/>
-      <c r="D26" s="94" t="s">
+      <c r="C26" s="177"/>
+      <c r="D26" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E26" s="95"/>
-      <c r="F26" s="94" t="s">
+      <c r="E26" s="117"/>
+      <c r="F26" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G26" s="95"/>
+      <c r="G26" s="117"/>
       <c r="H26" s="17" t="s">
         <v>103</v>
       </c>
@@ -4373,29 +4368,29 @@
       <c r="V26" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W26" s="100" t="s">
+      <c r="W26" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X26" s="101"/>
-      <c r="Y26" s="101"/>
-      <c r="Z26" s="102"/>
+      <c r="X26" s="70"/>
+      <c r="Y26" s="70"/>
+      <c r="Z26" s="71"/>
     </row>
     <row r="27" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="92" t="s">
+      <c r="B27" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C27" s="93"/>
-      <c r="D27" s="94" t="s">
+      <c r="C27" s="177"/>
+      <c r="D27" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E27" s="95"/>
-      <c r="F27" s="94" t="s">
+      <c r="E27" s="117"/>
+      <c r="F27" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G27" s="95"/>
+      <c r="G27" s="117"/>
       <c r="H27" s="17" t="s">
         <v>103</v>
       </c>
@@ -4441,29 +4436,29 @@
       <c r="V27" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W27" s="100" t="s">
+      <c r="W27" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X27" s="101"/>
-      <c r="Y27" s="101"/>
-      <c r="Z27" s="102"/>
+      <c r="X27" s="70"/>
+      <c r="Y27" s="70"/>
+      <c r="Z27" s="71"/>
     </row>
     <row r="28" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="92" t="s">
+      <c r="B28" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C28" s="93"/>
-      <c r="D28" s="94" t="s">
+      <c r="C28" s="177"/>
+      <c r="D28" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E28" s="95"/>
-      <c r="F28" s="94" t="s">
+      <c r="E28" s="117"/>
+      <c r="F28" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G28" s="95"/>
+      <c r="G28" s="117"/>
       <c r="H28" s="17" t="s">
         <v>103</v>
       </c>
@@ -4509,29 +4504,29 @@
       <c r="V28" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W28" s="100" t="s">
+      <c r="W28" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X28" s="101"/>
-      <c r="Y28" s="101"/>
-      <c r="Z28" s="102"/>
+      <c r="X28" s="70"/>
+      <c r="Y28" s="70"/>
+      <c r="Z28" s="71"/>
     </row>
     <row r="29" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="92" t="s">
+      <c r="B29" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="93"/>
-      <c r="D29" s="94" t="s">
+      <c r="C29" s="177"/>
+      <c r="D29" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E29" s="95"/>
-      <c r="F29" s="94" t="s">
+      <c r="E29" s="117"/>
+      <c r="F29" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G29" s="95"/>
+      <c r="G29" s="117"/>
       <c r="H29" s="17" t="s">
         <v>103</v>
       </c>
@@ -4577,29 +4572,29 @@
       <c r="V29" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W29" s="100" t="s">
+      <c r="W29" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X29" s="101"/>
-      <c r="Y29" s="101"/>
-      <c r="Z29" s="102"/>
+      <c r="X29" s="70"/>
+      <c r="Y29" s="70"/>
+      <c r="Z29" s="71"/>
     </row>
     <row r="30" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="92" t="s">
+      <c r="B30" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="93"/>
-      <c r="D30" s="94" t="s">
+      <c r="C30" s="177"/>
+      <c r="D30" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E30" s="95"/>
-      <c r="F30" s="94" t="s">
+      <c r="E30" s="117"/>
+      <c r="F30" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G30" s="95"/>
+      <c r="G30" s="117"/>
       <c r="H30" s="17" t="s">
         <v>103</v>
       </c>
@@ -4645,29 +4640,29 @@
       <c r="V30" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W30" s="100" t="s">
+      <c r="W30" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X30" s="101"/>
-      <c r="Y30" s="101"/>
-      <c r="Z30" s="102"/>
+      <c r="X30" s="70"/>
+      <c r="Y30" s="70"/>
+      <c r="Z30" s="71"/>
     </row>
     <row r="31" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="92" t="s">
+      <c r="B31" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="93"/>
-      <c r="D31" s="94" t="s">
+      <c r="C31" s="177"/>
+      <c r="D31" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E31" s="95"/>
-      <c r="F31" s="94" t="s">
+      <c r="E31" s="117"/>
+      <c r="F31" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G31" s="95"/>
+      <c r="G31" s="117"/>
       <c r="H31" s="17" t="s">
         <v>103</v>
       </c>
@@ -4713,29 +4708,29 @@
       <c r="V31" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W31" s="100" t="s">
+      <c r="W31" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X31" s="101"/>
-      <c r="Y31" s="101"/>
-      <c r="Z31" s="102"/>
+      <c r="X31" s="70"/>
+      <c r="Y31" s="70"/>
+      <c r="Z31" s="71"/>
     </row>
     <row r="32" spans="1:29" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="92" t="s">
+      <c r="B32" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="93"/>
-      <c r="D32" s="94" t="s">
+      <c r="C32" s="177"/>
+      <c r="D32" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E32" s="95"/>
-      <c r="F32" s="94" t="s">
+      <c r="E32" s="117"/>
+      <c r="F32" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G32" s="95"/>
+      <c r="G32" s="117"/>
       <c r="H32" s="17" t="s">
         <v>103</v>
       </c>
@@ -4781,29 +4776,29 @@
       <c r="V32" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W32" s="100" t="s">
+      <c r="W32" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X32" s="101"/>
-      <c r="Y32" s="101"/>
-      <c r="Z32" s="102"/>
+      <c r="X32" s="70"/>
+      <c r="Y32" s="70"/>
+      <c r="Z32" s="71"/>
     </row>
     <row r="33" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="92" t="s">
+      <c r="B33" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C33" s="93"/>
-      <c r="D33" s="94" t="s">
+      <c r="C33" s="177"/>
+      <c r="D33" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E33" s="95"/>
-      <c r="F33" s="94" t="s">
+      <c r="E33" s="117"/>
+      <c r="F33" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G33" s="95"/>
+      <c r="G33" s="117"/>
       <c r="H33" s="17" t="s">
         <v>103</v>
       </c>
@@ -4849,29 +4844,29 @@
       <c r="V33" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W33" s="100" t="s">
+      <c r="W33" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X33" s="101"/>
-      <c r="Y33" s="101"/>
-      <c r="Z33" s="102"/>
+      <c r="X33" s="70"/>
+      <c r="Y33" s="70"/>
+      <c r="Z33" s="71"/>
     </row>
     <row r="34" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C34" s="93"/>
-      <c r="D34" s="94" t="s">
+      <c r="C34" s="177"/>
+      <c r="D34" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E34" s="95"/>
-      <c r="F34" s="94" t="s">
+      <c r="E34" s="117"/>
+      <c r="F34" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G34" s="95"/>
+      <c r="G34" s="117"/>
       <c r="H34" s="17" t="s">
         <v>103</v>
       </c>
@@ -4917,29 +4912,29 @@
       <c r="V34" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W34" s="100" t="s">
+      <c r="W34" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X34" s="101"/>
-      <c r="Y34" s="101"/>
-      <c r="Z34" s="102"/>
+      <c r="X34" s="70"/>
+      <c r="Y34" s="70"/>
+      <c r="Z34" s="71"/>
     </row>
     <row r="35" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="92" t="s">
+      <c r="B35" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C35" s="93"/>
-      <c r="D35" s="94" t="s">
+      <c r="C35" s="177"/>
+      <c r="D35" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E35" s="95"/>
-      <c r="F35" s="94" t="s">
+      <c r="E35" s="117"/>
+      <c r="F35" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G35" s="95"/>
+      <c r="G35" s="117"/>
       <c r="H35" s="17" t="s">
         <v>103</v>
       </c>
@@ -4985,29 +4980,29 @@
       <c r="V35" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W35" s="100" t="s">
+      <c r="W35" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X35" s="101"/>
-      <c r="Y35" s="101"/>
-      <c r="Z35" s="102"/>
+      <c r="X35" s="70"/>
+      <c r="Y35" s="70"/>
+      <c r="Z35" s="71"/>
     </row>
     <row r="36" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="92" t="s">
+      <c r="B36" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C36" s="93"/>
-      <c r="D36" s="94" t="s">
+      <c r="C36" s="177"/>
+      <c r="D36" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E36" s="95"/>
-      <c r="F36" s="94" t="s">
+      <c r="E36" s="117"/>
+      <c r="F36" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G36" s="95"/>
+      <c r="G36" s="117"/>
       <c r="H36" s="17" t="s">
         <v>103</v>
       </c>
@@ -5053,29 +5048,29 @@
       <c r="V36" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W36" s="100" t="s">
+      <c r="W36" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X36" s="101"/>
-      <c r="Y36" s="101"/>
-      <c r="Z36" s="102"/>
+      <c r="X36" s="70"/>
+      <c r="Y36" s="70"/>
+      <c r="Z36" s="71"/>
     </row>
     <row r="37" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="B37" s="92" t="s">
+      <c r="B37" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C37" s="93"/>
-      <c r="D37" s="94" t="s">
+      <c r="C37" s="177"/>
+      <c r="D37" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E37" s="95"/>
-      <c r="F37" s="94" t="s">
+      <c r="E37" s="117"/>
+      <c r="F37" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G37" s="95"/>
+      <c r="G37" s="117"/>
       <c r="H37" s="17" t="s">
         <v>103</v>
       </c>
@@ -5121,29 +5116,29 @@
       <c r="V37" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W37" s="100" t="s">
+      <c r="W37" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X37" s="101"/>
-      <c r="Y37" s="101"/>
-      <c r="Z37" s="102"/>
+      <c r="X37" s="70"/>
+      <c r="Y37" s="70"/>
+      <c r="Z37" s="71"/>
     </row>
     <row r="38" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="92" t="s">
+      <c r="B38" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C38" s="93"/>
-      <c r="D38" s="94" t="s">
+      <c r="C38" s="177"/>
+      <c r="D38" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E38" s="95"/>
-      <c r="F38" s="94" t="s">
+      <c r="E38" s="117"/>
+      <c r="F38" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G38" s="95"/>
+      <c r="G38" s="117"/>
       <c r="H38" s="17" t="s">
         <v>103</v>
       </c>
@@ -5189,29 +5184,29 @@
       <c r="V38" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W38" s="100" t="s">
+      <c r="W38" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X38" s="101"/>
-      <c r="Y38" s="101"/>
-      <c r="Z38" s="102"/>
+      <c r="X38" s="70"/>
+      <c r="Y38" s="70"/>
+      <c r="Z38" s="71"/>
     </row>
     <row r="39" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="B39" s="92" t="s">
+      <c r="B39" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C39" s="93"/>
-      <c r="D39" s="94" t="s">
+      <c r="C39" s="177"/>
+      <c r="D39" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E39" s="95"/>
-      <c r="F39" s="94" t="s">
+      <c r="E39" s="117"/>
+      <c r="F39" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G39" s="95"/>
+      <c r="G39" s="117"/>
       <c r="H39" s="17" t="s">
         <v>103</v>
       </c>
@@ -5257,29 +5252,29 @@
       <c r="V39" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W39" s="100" t="s">
+      <c r="W39" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X39" s="101"/>
-      <c r="Y39" s="101"/>
-      <c r="Z39" s="102"/>
+      <c r="X39" s="70"/>
+      <c r="Y39" s="70"/>
+      <c r="Z39" s="71"/>
     </row>
     <row r="40" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="92" t="s">
+      <c r="B40" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C40" s="93"/>
-      <c r="D40" s="94" t="s">
+      <c r="C40" s="177"/>
+      <c r="D40" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E40" s="95"/>
-      <c r="F40" s="94" t="s">
+      <c r="E40" s="117"/>
+      <c r="F40" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G40" s="95"/>
+      <c r="G40" s="117"/>
       <c r="H40" s="17" t="s">
         <v>103</v>
       </c>
@@ -5325,29 +5320,29 @@
       <c r="V40" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W40" s="100" t="s">
+      <c r="W40" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X40" s="101"/>
-      <c r="Y40" s="101"/>
-      <c r="Z40" s="102"/>
+      <c r="X40" s="70"/>
+      <c r="Y40" s="70"/>
+      <c r="Z40" s="71"/>
     </row>
     <row r="41" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="92" t="s">
+      <c r="B41" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C41" s="93"/>
-      <c r="D41" s="94" t="s">
+      <c r="C41" s="177"/>
+      <c r="D41" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E41" s="95"/>
-      <c r="F41" s="94" t="s">
+      <c r="E41" s="117"/>
+      <c r="F41" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G41" s="95"/>
+      <c r="G41" s="117"/>
       <c r="H41" s="17" t="s">
         <v>103</v>
       </c>
@@ -5393,29 +5388,29 @@
       <c r="V41" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W41" s="100" t="s">
+      <c r="W41" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X41" s="101"/>
-      <c r="Y41" s="101"/>
-      <c r="Z41" s="102"/>
+      <c r="X41" s="70"/>
+      <c r="Y41" s="70"/>
+      <c r="Z41" s="71"/>
     </row>
     <row r="42" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="B42" s="92" t="s">
+      <c r="B42" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C42" s="93"/>
-      <c r="D42" s="94" t="s">
+      <c r="C42" s="177"/>
+      <c r="D42" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E42" s="95"/>
-      <c r="F42" s="94" t="s">
+      <c r="E42" s="117"/>
+      <c r="F42" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G42" s="95"/>
+      <c r="G42" s="117"/>
       <c r="H42" s="17" t="s">
         <v>103</v>
       </c>
@@ -5461,29 +5456,29 @@
       <c r="V42" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W42" s="100" t="s">
+      <c r="W42" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X42" s="101"/>
-      <c r="Y42" s="101"/>
-      <c r="Z42" s="102"/>
+      <c r="X42" s="70"/>
+      <c r="Y42" s="70"/>
+      <c r="Z42" s="71"/>
     </row>
     <row r="43" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="B43" s="92" t="s">
+      <c r="B43" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C43" s="93"/>
-      <c r="D43" s="94" t="s">
+      <c r="C43" s="177"/>
+      <c r="D43" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E43" s="95"/>
-      <c r="F43" s="94" t="s">
+      <c r="E43" s="117"/>
+      <c r="F43" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G43" s="95"/>
+      <c r="G43" s="117"/>
       <c r="H43" s="17" t="s">
         <v>103</v>
       </c>
@@ -5529,29 +5524,29 @@
       <c r="V43" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W43" s="100" t="s">
+      <c r="W43" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X43" s="101"/>
-      <c r="Y43" s="101"/>
-      <c r="Z43" s="102"/>
+      <c r="X43" s="70"/>
+      <c r="Y43" s="70"/>
+      <c r="Z43" s="71"/>
     </row>
     <row r="44" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="B44" s="92" t="s">
+      <c r="B44" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C44" s="93"/>
-      <c r="D44" s="94" t="s">
+      <c r="C44" s="177"/>
+      <c r="D44" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E44" s="95"/>
-      <c r="F44" s="94" t="s">
+      <c r="E44" s="117"/>
+      <c r="F44" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G44" s="95"/>
+      <c r="G44" s="117"/>
       <c r="H44" s="17" t="s">
         <v>103</v>
       </c>
@@ -5597,29 +5592,29 @@
       <c r="V44" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W44" s="100" t="s">
+      <c r="W44" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X44" s="101"/>
-      <c r="Y44" s="101"/>
-      <c r="Z44" s="102"/>
+      <c r="X44" s="70"/>
+      <c r="Y44" s="70"/>
+      <c r="Z44" s="71"/>
     </row>
     <row r="45" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="B45" s="92" t="s">
+      <c r="B45" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C45" s="93"/>
-      <c r="D45" s="94" t="s">
+      <c r="C45" s="177"/>
+      <c r="D45" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E45" s="95"/>
-      <c r="F45" s="94" t="s">
+      <c r="E45" s="117"/>
+      <c r="F45" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G45" s="95"/>
+      <c r="G45" s="117"/>
       <c r="H45" s="17" t="s">
         <v>103</v>
       </c>
@@ -5665,29 +5660,29 @@
       <c r="V45" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W45" s="100" t="s">
+      <c r="W45" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X45" s="101"/>
-      <c r="Y45" s="101"/>
-      <c r="Z45" s="102"/>
+      <c r="X45" s="70"/>
+      <c r="Y45" s="70"/>
+      <c r="Z45" s="71"/>
     </row>
     <row r="46" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="B46" s="92" t="s">
+      <c r="B46" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C46" s="93"/>
-      <c r="D46" s="94" t="s">
+      <c r="C46" s="177"/>
+      <c r="D46" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E46" s="95"/>
-      <c r="F46" s="94" t="s">
+      <c r="E46" s="117"/>
+      <c r="F46" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G46" s="95"/>
+      <c r="G46" s="117"/>
       <c r="H46" s="17" t="s">
         <v>103</v>
       </c>
@@ -5733,29 +5728,29 @@
       <c r="V46" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W46" s="100" t="s">
+      <c r="W46" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X46" s="101"/>
-      <c r="Y46" s="101"/>
-      <c r="Z46" s="102"/>
+      <c r="X46" s="70"/>
+      <c r="Y46" s="70"/>
+      <c r="Z46" s="71"/>
     </row>
     <row r="47" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="B47" s="92" t="s">
+      <c r="B47" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="93"/>
-      <c r="D47" s="94" t="s">
+      <c r="C47" s="177"/>
+      <c r="D47" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E47" s="95"/>
-      <c r="F47" s="94" t="s">
+      <c r="E47" s="117"/>
+      <c r="F47" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G47" s="95"/>
+      <c r="G47" s="117"/>
       <c r="H47" s="17" t="s">
         <v>103</v>
       </c>
@@ -5801,29 +5796,29 @@
       <c r="V47" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W47" s="100" t="s">
+      <c r="W47" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X47" s="101"/>
-      <c r="Y47" s="101"/>
-      <c r="Z47" s="102"/>
+      <c r="X47" s="70"/>
+      <c r="Y47" s="70"/>
+      <c r="Z47" s="71"/>
     </row>
     <row r="48" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="B48" s="92" t="s">
+      <c r="B48" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C48" s="93"/>
-      <c r="D48" s="94" t="s">
+      <c r="C48" s="177"/>
+      <c r="D48" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E48" s="95"/>
-      <c r="F48" s="94" t="s">
+      <c r="E48" s="117"/>
+      <c r="F48" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G48" s="95"/>
+      <c r="G48" s="117"/>
       <c r="H48" s="17" t="s">
         <v>103</v>
       </c>
@@ -5869,29 +5864,29 @@
       <c r="V48" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W48" s="100" t="s">
+      <c r="W48" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X48" s="101"/>
-      <c r="Y48" s="101"/>
-      <c r="Z48" s="102"/>
+      <c r="X48" s="70"/>
+      <c r="Y48" s="70"/>
+      <c r="Z48" s="71"/>
     </row>
     <row r="49" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="B49" s="92" t="s">
+      <c r="B49" s="176" t="s">
         <v>100</v>
       </c>
-      <c r="C49" s="93"/>
-      <c r="D49" s="94" t="s">
+      <c r="C49" s="177"/>
+      <c r="D49" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E49" s="95"/>
-      <c r="F49" s="94" t="s">
+      <c r="E49" s="117"/>
+      <c r="F49" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G49" s="95"/>
+      <c r="G49" s="117"/>
       <c r="H49" s="17" t="s">
         <v>103</v>
       </c>
@@ -5937,29 +5932,29 @@
       <c r="V49" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="W49" s="100" t="s">
+      <c r="W49" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="X49" s="101"/>
-      <c r="Y49" s="101"/>
-      <c r="Z49" s="102"/>
+      <c r="X49" s="70"/>
+      <c r="Y49" s="70"/>
+      <c r="Z49" s="71"/>
     </row>
     <row r="50" spans="1:26" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A50" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="B50" s="103" t="s">
+      <c r="B50" s="163" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="104"/>
-      <c r="D50" s="105" t="s">
+      <c r="C50" s="164"/>
+      <c r="D50" s="165" t="s">
         <v>101</v>
       </c>
-      <c r="E50" s="106"/>
-      <c r="F50" s="105" t="s">
+      <c r="E50" s="166"/>
+      <c r="F50" s="165" t="s">
         <v>102</v>
       </c>
-      <c r="G50" s="106"/>
+      <c r="G50" s="166"/>
       <c r="H50" s="24" t="s">
         <v>103</v>
       </c>
@@ -6005,31 +6000,31 @@
       <c r="V50" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="W50" s="154" t="s">
+      <c r="W50" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="X50" s="203"/>
-      <c r="Y50" s="203"/>
-      <c r="Z50" s="204"/>
+      <c r="X50" s="46"/>
+      <c r="Y50" s="46"/>
+      <c r="Z50" s="47"/>
     </row>
     <row r="51" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="107" t="s">
+      <c r="A51" s="167" t="s">
         <v>60</v>
       </c>
-      <c r="B51" s="108"/>
-      <c r="C51" s="108"/>
-      <c r="D51" s="108"/>
-      <c r="E51" s="109"/>
-      <c r="F51" s="115" t="s">
+      <c r="B51" s="168"/>
+      <c r="C51" s="168"/>
+      <c r="D51" s="168"/>
+      <c r="E51" s="169"/>
+      <c r="F51" s="161" t="s">
         <v>61</v>
       </c>
-      <c r="G51" s="116"/>
-      <c r="H51" s="116"/>
-      <c r="I51" s="116"/>
-      <c r="J51" s="116"/>
-      <c r="K51" s="116"/>
-      <c r="L51" s="116"/>
-      <c r="M51" s="117"/>
+      <c r="G51" s="84"/>
+      <c r="H51" s="84"/>
+      <c r="I51" s="84"/>
+      <c r="J51" s="84"/>
+      <c r="K51" s="84"/>
+      <c r="L51" s="84"/>
+      <c r="M51" s="162"/>
       <c r="N51" s="27" t="s">
         <v>104</v>
       </c>
@@ -6057,27 +6052,27 @@
       <c r="V51" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="W51" s="205"/>
-      <c r="X51" s="206"/>
-      <c r="Y51" s="206"/>
-      <c r="Z51" s="207"/>
+      <c r="W51" s="48"/>
+      <c r="X51" s="49"/>
+      <c r="Y51" s="49"/>
+      <c r="Z51" s="50"/>
     </row>
     <row r="52" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="110"/>
-      <c r="B52" s="111"/>
-      <c r="C52" s="111"/>
-      <c r="D52" s="111"/>
-      <c r="E52" s="112"/>
-      <c r="F52" s="118" t="s">
+      <c r="A52" s="170"/>
+      <c r="B52" s="171"/>
+      <c r="C52" s="171"/>
+      <c r="D52" s="171"/>
+      <c r="E52" s="172"/>
+      <c r="F52" s="138" t="s">
         <v>62</v>
       </c>
-      <c r="G52" s="119"/>
-      <c r="H52" s="119"/>
-      <c r="I52" s="119"/>
-      <c r="J52" s="119"/>
-      <c r="K52" s="119"/>
-      <c r="L52" s="119"/>
-      <c r="M52" s="120"/>
+      <c r="G52" s="85"/>
+      <c r="H52" s="85"/>
+      <c r="I52" s="85"/>
+      <c r="J52" s="85"/>
+      <c r="K52" s="85"/>
+      <c r="L52" s="85"/>
+      <c r="M52" s="139"/>
       <c r="N52" s="26" t="s">
         <v>104</v>
       </c>
@@ -6105,27 +6100,27 @@
       <c r="V52" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="W52" s="208"/>
-      <c r="X52" s="209"/>
-      <c r="Y52" s="209"/>
-      <c r="Z52" s="210"/>
+      <c r="W52" s="51"/>
+      <c r="X52" s="52"/>
+      <c r="Y52" s="52"/>
+      <c r="Z52" s="53"/>
     </row>
     <row r="53" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="110"/>
-      <c r="B53" s="111"/>
-      <c r="C53" s="111"/>
-      <c r="D53" s="111"/>
-      <c r="E53" s="112"/>
-      <c r="F53" s="118" t="s">
+      <c r="A53" s="170"/>
+      <c r="B53" s="171"/>
+      <c r="C53" s="171"/>
+      <c r="D53" s="171"/>
+      <c r="E53" s="172"/>
+      <c r="F53" s="138" t="s">
         <v>63</v>
       </c>
-      <c r="G53" s="119"/>
-      <c r="H53" s="119"/>
-      <c r="I53" s="119"/>
-      <c r="J53" s="119"/>
-      <c r="K53" s="119"/>
-      <c r="L53" s="119"/>
-      <c r="M53" s="120"/>
+      <c r="G53" s="85"/>
+      <c r="H53" s="85"/>
+      <c r="I53" s="85"/>
+      <c r="J53" s="85"/>
+      <c r="K53" s="85"/>
+      <c r="L53" s="85"/>
+      <c r="M53" s="139"/>
       <c r="N53" s="26" t="s">
         <v>104</v>
       </c>
@@ -6153,27 +6148,27 @@
       <c r="V53" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="W53" s="208"/>
-      <c r="X53" s="209"/>
-      <c r="Y53" s="209"/>
-      <c r="Z53" s="210"/>
+      <c r="W53" s="51"/>
+      <c r="X53" s="52"/>
+      <c r="Y53" s="52"/>
+      <c r="Z53" s="53"/>
     </row>
     <row r="54" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="110"/>
-      <c r="B54" s="111"/>
-      <c r="C54" s="111"/>
-      <c r="D54" s="111"/>
-      <c r="E54" s="112"/>
-      <c r="F54" s="118" t="s">
+      <c r="A54" s="170"/>
+      <c r="B54" s="171"/>
+      <c r="C54" s="171"/>
+      <c r="D54" s="171"/>
+      <c r="E54" s="172"/>
+      <c r="F54" s="138" t="s">
         <v>64</v>
       </c>
-      <c r="G54" s="119"/>
-      <c r="H54" s="119"/>
-      <c r="I54" s="119"/>
-      <c r="J54" s="119"/>
-      <c r="K54" s="119"/>
-      <c r="L54" s="119"/>
-      <c r="M54" s="120"/>
+      <c r="G54" s="85"/>
+      <c r="H54" s="85"/>
+      <c r="I54" s="85"/>
+      <c r="J54" s="85"/>
+      <c r="K54" s="85"/>
+      <c r="L54" s="85"/>
+      <c r="M54" s="139"/>
       <c r="N54" s="26" t="s">
         <v>104</v>
       </c>
@@ -6201,27 +6196,27 @@
       <c r="V54" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="W54" s="208"/>
-      <c r="X54" s="209"/>
-      <c r="Y54" s="209"/>
-      <c r="Z54" s="210"/>
+      <c r="W54" s="51"/>
+      <c r="X54" s="52"/>
+      <c r="Y54" s="52"/>
+      <c r="Z54" s="53"/>
     </row>
     <row r="55" spans="1:26" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="113"/>
-      <c r="B55" s="45"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="45"/>
-      <c r="E55" s="114"/>
-      <c r="F55" s="130" t="s">
+      <c r="A55" s="173"/>
+      <c r="B55" s="174"/>
+      <c r="C55" s="174"/>
+      <c r="D55" s="174"/>
+      <c r="E55" s="175"/>
+      <c r="F55" s="147" t="s">
         <v>65</v>
       </c>
-      <c r="G55" s="131"/>
-      <c r="H55" s="131"/>
-      <c r="I55" s="131"/>
-      <c r="J55" s="131"/>
-      <c r="K55" s="131"/>
-      <c r="L55" s="131"/>
-      <c r="M55" s="132"/>
+      <c r="G55" s="148"/>
+      <c r="H55" s="148"/>
+      <c r="I55" s="148"/>
+      <c r="J55" s="148"/>
+      <c r="K55" s="148"/>
+      <c r="L55" s="148"/>
+      <c r="M55" s="149"/>
       <c r="N55" s="31" t="s">
         <v>104</v>
       </c>
@@ -6249,82 +6244,82 @@
       <c r="V55" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="W55" s="211"/>
-      <c r="X55" s="212"/>
-      <c r="Y55" s="212"/>
-      <c r="Z55" s="213"/>
+      <c r="W55" s="54"/>
+      <c r="X55" s="55"/>
+      <c r="Y55" s="55"/>
+      <c r="Z55" s="56"/>
     </row>
     <row r="56" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="133" t="s">
+      <c r="A56" s="89" t="s">
         <v>66</v>
       </c>
-      <c r="B56" s="122"/>
-      <c r="C56" s="122"/>
-      <c r="D56" s="122"/>
-      <c r="E56" s="123"/>
-      <c r="F56" s="134" t="s">
+      <c r="B56" s="90"/>
+      <c r="C56" s="90"/>
+      <c r="D56" s="90"/>
+      <c r="E56" s="91"/>
+      <c r="F56" s="104" t="s">
         <v>75</v>
       </c>
-      <c r="G56" s="135"/>
-      <c r="H56" s="138" t="s">
+      <c r="G56" s="150"/>
+      <c r="H56" s="153" t="s">
         <v>36</v>
       </c>
-      <c r="I56" s="140" t="s">
+      <c r="I56" s="155" t="s">
         <v>76</v>
       </c>
-      <c r="J56" s="141"/>
-      <c r="K56" s="141"/>
-      <c r="L56" s="141"/>
-      <c r="M56" s="141"/>
-      <c r="N56" s="141"/>
-      <c r="O56" s="142"/>
-      <c r="P56" s="115" t="s">
+      <c r="J56" s="156"/>
+      <c r="K56" s="156"/>
+      <c r="L56" s="156"/>
+      <c r="M56" s="156"/>
+      <c r="N56" s="156"/>
+      <c r="O56" s="157"/>
+      <c r="P56" s="161" t="s">
         <v>77</v>
       </c>
-      <c r="Q56" s="116"/>
-      <c r="R56" s="116"/>
-      <c r="S56" s="116"/>
-      <c r="T56" s="116"/>
-      <c r="U56" s="116"/>
-      <c r="V56" s="116"/>
-      <c r="W56" s="116"/>
-      <c r="X56" s="116"/>
-      <c r="Y56" s="116"/>
-      <c r="Z56" s="117"/>
+      <c r="Q56" s="84"/>
+      <c r="R56" s="84"/>
+      <c r="S56" s="84"/>
+      <c r="T56" s="84"/>
+      <c r="U56" s="84"/>
+      <c r="V56" s="84"/>
+      <c r="W56" s="84"/>
+      <c r="X56" s="84"/>
+      <c r="Y56" s="84"/>
+      <c r="Z56" s="162"/>
     </row>
     <row r="57" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B57" s="121" t="s">
+      <c r="B57" s="146" t="s">
         <v>67</v>
       </c>
-      <c r="C57" s="122"/>
-      <c r="D57" s="122"/>
-      <c r="E57" s="123"/>
-      <c r="F57" s="136"/>
-      <c r="G57" s="137"/>
-      <c r="H57" s="139"/>
-      <c r="I57" s="143"/>
-      <c r="J57" s="144"/>
-      <c r="K57" s="144"/>
-      <c r="L57" s="144"/>
-      <c r="M57" s="144"/>
-      <c r="N57" s="144"/>
-      <c r="O57" s="145"/>
-      <c r="P57" s="118" t="s">
+      <c r="C57" s="90"/>
+      <c r="D57" s="90"/>
+      <c r="E57" s="91"/>
+      <c r="F57" s="151"/>
+      <c r="G57" s="152"/>
+      <c r="H57" s="154"/>
+      <c r="I57" s="158"/>
+      <c r="J57" s="159"/>
+      <c r="K57" s="159"/>
+      <c r="L57" s="159"/>
+      <c r="M57" s="159"/>
+      <c r="N57" s="159"/>
+      <c r="O57" s="160"/>
+      <c r="P57" s="138" t="s">
         <v>78</v>
       </c>
-      <c r="Q57" s="119"/>
-      <c r="R57" s="119"/>
-      <c r="S57" s="119"/>
-      <c r="T57" s="119"/>
-      <c r="U57" s="119"/>
-      <c r="V57" s="119"/>
-      <c r="W57" s="119"/>
-      <c r="X57" s="119"/>
-      <c r="Y57" s="119"/>
-      <c r="Z57" s="120"/>
+      <c r="Q57" s="85"/>
+      <c r="R57" s="85"/>
+      <c r="S57" s="85"/>
+      <c r="T57" s="85"/>
+      <c r="U57" s="85"/>
+      <c r="V57" s="85"/>
+      <c r="W57" s="85"/>
+      <c r="X57" s="85"/>
+      <c r="Y57" s="85"/>
+      <c r="Z57" s="139"/>
     </row>
     <row r="58" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="26" t="s">
@@ -6333,38 +6328,38 @@
       <c r="B58" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C58" s="94" t="s">
+      <c r="C58" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="D58" s="101"/>
-      <c r="E58" s="102"/>
-      <c r="F58" s="100" t="s">
+      <c r="D58" s="70"/>
+      <c r="E58" s="71"/>
+      <c r="F58" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="G58" s="95"/>
+      <c r="G58" s="117"/>
       <c r="H58" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I58" s="124" t="s">
+      <c r="I58" s="118" t="s">
         <v>108</v>
       </c>
-      <c r="J58" s="125"/>
-      <c r="K58" s="125"/>
-      <c r="L58" s="125"/>
-      <c r="M58" s="125"/>
-      <c r="N58" s="125"/>
-      <c r="O58" s="126"/>
-      <c r="P58" s="127"/>
-      <c r="Q58" s="128"/>
-      <c r="R58" s="128"/>
-      <c r="S58" s="128"/>
-      <c r="T58" s="128"/>
-      <c r="U58" s="128"/>
-      <c r="V58" s="128"/>
-      <c r="W58" s="128"/>
-      <c r="X58" s="128"/>
-      <c r="Y58" s="128"/>
-      <c r="Z58" s="129"/>
+      <c r="J58" s="119"/>
+      <c r="K58" s="119"/>
+      <c r="L58" s="119"/>
+      <c r="M58" s="119"/>
+      <c r="N58" s="119"/>
+      <c r="O58" s="120"/>
+      <c r="P58" s="121"/>
+      <c r="Q58" s="122"/>
+      <c r="R58" s="122"/>
+      <c r="S58" s="122"/>
+      <c r="T58" s="122"/>
+      <c r="U58" s="122"/>
+      <c r="V58" s="122"/>
+      <c r="W58" s="122"/>
+      <c r="X58" s="122"/>
+      <c r="Y58" s="122"/>
+      <c r="Z58" s="125"/>
     </row>
     <row r="59" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="26" t="s">
@@ -6373,40 +6368,40 @@
       <c r="B59" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C59" s="94" t="s">
+      <c r="C59" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="D59" s="101"/>
-      <c r="E59" s="102"/>
-      <c r="F59" s="100" t="s">
+      <c r="D59" s="70"/>
+      <c r="E59" s="71"/>
+      <c r="F59" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="G59" s="95"/>
+      <c r="G59" s="117"/>
       <c r="H59" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I59" s="124" t="s">
+      <c r="I59" s="118" t="s">
         <v>108</v>
       </c>
-      <c r="J59" s="125"/>
-      <c r="K59" s="125"/>
-      <c r="L59" s="125"/>
-      <c r="M59" s="125"/>
-      <c r="N59" s="125"/>
-      <c r="O59" s="126"/>
-      <c r="P59" s="118" t="s">
+      <c r="J59" s="119"/>
+      <c r="K59" s="119"/>
+      <c r="L59" s="119"/>
+      <c r="M59" s="119"/>
+      <c r="N59" s="119"/>
+      <c r="O59" s="120"/>
+      <c r="P59" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="Q59" s="119"/>
-      <c r="R59" s="119"/>
-      <c r="S59" s="119"/>
-      <c r="T59" s="119"/>
-      <c r="U59" s="119"/>
-      <c r="V59" s="119"/>
-      <c r="W59" s="119"/>
-      <c r="X59" s="119"/>
-      <c r="Y59" s="119"/>
-      <c r="Z59" s="120"/>
+      <c r="Q59" s="85"/>
+      <c r="R59" s="85"/>
+      <c r="S59" s="85"/>
+      <c r="T59" s="85"/>
+      <c r="U59" s="85"/>
+      <c r="V59" s="85"/>
+      <c r="W59" s="85"/>
+      <c r="X59" s="85"/>
+      <c r="Y59" s="85"/>
+      <c r="Z59" s="139"/>
     </row>
     <row r="60" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="26" t="s">
@@ -6415,38 +6410,38 @@
       <c r="B60" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C60" s="94" t="s">
+      <c r="C60" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="D60" s="101"/>
-      <c r="E60" s="102"/>
-      <c r="F60" s="100" t="s">
+      <c r="D60" s="70"/>
+      <c r="E60" s="71"/>
+      <c r="F60" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="G60" s="95"/>
+      <c r="G60" s="117"/>
       <c r="H60" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I60" s="124" t="s">
+      <c r="I60" s="118" t="s">
         <v>108</v>
       </c>
-      <c r="J60" s="125"/>
-      <c r="K60" s="125"/>
-      <c r="L60" s="125"/>
-      <c r="M60" s="125"/>
-      <c r="N60" s="125"/>
-      <c r="O60" s="126"/>
-      <c r="P60" s="118"/>
-      <c r="Q60" s="119"/>
-      <c r="R60" s="119"/>
-      <c r="S60" s="119"/>
-      <c r="T60" s="119"/>
-      <c r="U60" s="119"/>
-      <c r="V60" s="119"/>
-      <c r="W60" s="119"/>
-      <c r="X60" s="119"/>
-      <c r="Y60" s="119"/>
-      <c r="Z60" s="120"/>
+      <c r="J60" s="119"/>
+      <c r="K60" s="119"/>
+      <c r="L60" s="119"/>
+      <c r="M60" s="119"/>
+      <c r="N60" s="119"/>
+      <c r="O60" s="120"/>
+      <c r="P60" s="138"/>
+      <c r="Q60" s="85"/>
+      <c r="R60" s="85"/>
+      <c r="S60" s="85"/>
+      <c r="T60" s="85"/>
+      <c r="U60" s="85"/>
+      <c r="V60" s="85"/>
+      <c r="W60" s="85"/>
+      <c r="X60" s="85"/>
+      <c r="Y60" s="85"/>
+      <c r="Z60" s="139"/>
     </row>
     <row r="61" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="26" t="s">
@@ -6455,40 +6450,40 @@
       <c r="B61" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C61" s="94" t="s">
+      <c r="C61" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="D61" s="101"/>
-      <c r="E61" s="102"/>
-      <c r="F61" s="100" t="s">
+      <c r="D61" s="70"/>
+      <c r="E61" s="71"/>
+      <c r="F61" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="G61" s="95"/>
+      <c r="G61" s="117"/>
       <c r="H61" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I61" s="124" t="s">
+      <c r="I61" s="118" t="s">
         <v>108</v>
       </c>
-      <c r="J61" s="125"/>
-      <c r="K61" s="125"/>
-      <c r="L61" s="125"/>
-      <c r="M61" s="125"/>
-      <c r="N61" s="125"/>
-      <c r="O61" s="126"/>
-      <c r="P61" s="118" t="s">
+      <c r="J61" s="119"/>
+      <c r="K61" s="119"/>
+      <c r="L61" s="119"/>
+      <c r="M61" s="119"/>
+      <c r="N61" s="119"/>
+      <c r="O61" s="120"/>
+      <c r="P61" s="138" t="s">
         <v>80</v>
       </c>
-      <c r="Q61" s="119"/>
-      <c r="R61" s="119"/>
-      <c r="S61" s="119"/>
-      <c r="T61" s="119"/>
-      <c r="U61" s="119"/>
-      <c r="V61" s="119"/>
-      <c r="W61" s="119"/>
-      <c r="X61" s="119"/>
-      <c r="Y61" s="119"/>
-      <c r="Z61" s="120"/>
+      <c r="Q61" s="85"/>
+      <c r="R61" s="85"/>
+      <c r="S61" s="85"/>
+      <c r="T61" s="85"/>
+      <c r="U61" s="85"/>
+      <c r="V61" s="85"/>
+      <c r="W61" s="85"/>
+      <c r="X61" s="85"/>
+      <c r="Y61" s="85"/>
+      <c r="Z61" s="139"/>
     </row>
     <row r="62" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="26" t="s">
@@ -6497,38 +6492,38 @@
       <c r="B62" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C62" s="94" t="s">
+      <c r="C62" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="D62" s="101"/>
-      <c r="E62" s="102"/>
-      <c r="F62" s="100" t="s">
+      <c r="D62" s="70"/>
+      <c r="E62" s="71"/>
+      <c r="F62" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="G62" s="95"/>
+      <c r="G62" s="117"/>
       <c r="H62" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I62" s="124" t="s">
+      <c r="I62" s="118" t="s">
         <v>108</v>
       </c>
-      <c r="J62" s="125"/>
-      <c r="K62" s="125"/>
-      <c r="L62" s="125"/>
-      <c r="M62" s="125"/>
-      <c r="N62" s="125"/>
-      <c r="O62" s="126"/>
-      <c r="P62" s="146"/>
-      <c r="Q62" s="147"/>
-      <c r="R62" s="147"/>
-      <c r="S62" s="147"/>
-      <c r="T62" s="147"/>
-      <c r="U62" s="147"/>
-      <c r="V62" s="147"/>
-      <c r="W62" s="147"/>
-      <c r="X62" s="147"/>
-      <c r="Y62" s="147"/>
-      <c r="Z62" s="148"/>
+      <c r="J62" s="119"/>
+      <c r="K62" s="119"/>
+      <c r="L62" s="119"/>
+      <c r="M62" s="119"/>
+      <c r="N62" s="119"/>
+      <c r="O62" s="120"/>
+      <c r="P62" s="143"/>
+      <c r="Q62" s="144"/>
+      <c r="R62" s="144"/>
+      <c r="S62" s="144"/>
+      <c r="T62" s="144"/>
+      <c r="U62" s="144"/>
+      <c r="V62" s="144"/>
+      <c r="W62" s="144"/>
+      <c r="X62" s="144"/>
+      <c r="Y62" s="144"/>
+      <c r="Z62" s="145"/>
     </row>
     <row r="63" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="26" t="s">
@@ -6537,40 +6532,40 @@
       <c r="B63" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C63" s="94" t="s">
+      <c r="C63" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="D63" s="101"/>
-      <c r="E63" s="102"/>
-      <c r="F63" s="100" t="s">
+      <c r="D63" s="70"/>
+      <c r="E63" s="71"/>
+      <c r="F63" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="G63" s="95"/>
+      <c r="G63" s="117"/>
       <c r="H63" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I63" s="124" t="s">
+      <c r="I63" s="118" t="s">
         <v>108</v>
       </c>
-      <c r="J63" s="125"/>
-      <c r="K63" s="125"/>
-      <c r="L63" s="125"/>
-      <c r="M63" s="125"/>
-      <c r="N63" s="125"/>
-      <c r="O63" s="126"/>
-      <c r="P63" s="118" t="s">
+      <c r="J63" s="119"/>
+      <c r="K63" s="119"/>
+      <c r="L63" s="119"/>
+      <c r="M63" s="119"/>
+      <c r="N63" s="119"/>
+      <c r="O63" s="120"/>
+      <c r="P63" s="138" t="s">
         <v>81</v>
       </c>
-      <c r="Q63" s="119"/>
-      <c r="R63" s="119"/>
-      <c r="S63" s="119"/>
-      <c r="T63" s="119"/>
-      <c r="U63" s="119"/>
-      <c r="V63" s="119"/>
-      <c r="W63" s="119"/>
-      <c r="X63" s="119"/>
-      <c r="Y63" s="119"/>
-      <c r="Z63" s="120"/>
+      <c r="Q63" s="85"/>
+      <c r="R63" s="85"/>
+      <c r="S63" s="85"/>
+      <c r="T63" s="85"/>
+      <c r="U63" s="85"/>
+      <c r="V63" s="85"/>
+      <c r="W63" s="85"/>
+      <c r="X63" s="85"/>
+      <c r="Y63" s="85"/>
+      <c r="Z63" s="139"/>
     </row>
     <row r="64" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="26" t="s">
@@ -6579,38 +6574,38 @@
       <c r="B64" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C64" s="94" t="s">
+      <c r="C64" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="D64" s="101"/>
-      <c r="E64" s="102"/>
-      <c r="F64" s="100" t="s">
+      <c r="D64" s="70"/>
+      <c r="E64" s="71"/>
+      <c r="F64" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="G64" s="95"/>
+      <c r="G64" s="117"/>
       <c r="H64" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I64" s="124" t="s">
+      <c r="I64" s="118" t="s">
         <v>108</v>
       </c>
-      <c r="J64" s="125"/>
-      <c r="K64" s="125"/>
-      <c r="L64" s="125"/>
-      <c r="M64" s="125"/>
-      <c r="N64" s="125"/>
-      <c r="O64" s="126"/>
-      <c r="P64" s="164"/>
-      <c r="Q64" s="47"/>
-      <c r="R64" s="47"/>
-      <c r="S64" s="47"/>
-      <c r="T64" s="47"/>
-      <c r="U64" s="47"/>
-      <c r="V64" s="47"/>
-      <c r="W64" s="47"/>
-      <c r="X64" s="47"/>
-      <c r="Y64" s="47"/>
-      <c r="Z64" s="165"/>
+      <c r="J64" s="119"/>
+      <c r="K64" s="119"/>
+      <c r="L64" s="119"/>
+      <c r="M64" s="119"/>
+      <c r="N64" s="119"/>
+      <c r="O64" s="120"/>
+      <c r="P64" s="140"/>
+      <c r="Q64" s="141"/>
+      <c r="R64" s="141"/>
+      <c r="S64" s="141"/>
+      <c r="T64" s="141"/>
+      <c r="U64" s="141"/>
+      <c r="V64" s="141"/>
+      <c r="W64" s="141"/>
+      <c r="X64" s="141"/>
+      <c r="Y64" s="141"/>
+      <c r="Z64" s="142"/>
     </row>
     <row r="65" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="26" t="s">
@@ -6619,42 +6614,42 @@
       <c r="B65" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="C65" s="94" t="s">
+      <c r="C65" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="D65" s="101"/>
-      <c r="E65" s="102"/>
-      <c r="F65" s="100" t="s">
+      <c r="D65" s="70"/>
+      <c r="E65" s="71"/>
+      <c r="F65" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="G65" s="95"/>
+      <c r="G65" s="117"/>
       <c r="H65" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="I65" s="124" t="s">
+      <c r="I65" s="118" t="s">
         <v>108</v>
       </c>
-      <c r="J65" s="125"/>
-      <c r="K65" s="125"/>
-      <c r="L65" s="125"/>
-      <c r="M65" s="125"/>
-      <c r="N65" s="125"/>
-      <c r="O65" s="126"/>
-      <c r="P65" s="127" t="s">
+      <c r="J65" s="119"/>
+      <c r="K65" s="119"/>
+      <c r="L65" s="119"/>
+      <c r="M65" s="119"/>
+      <c r="N65" s="119"/>
+      <c r="O65" s="120"/>
+      <c r="P65" s="121" t="s">
         <v>82</v>
       </c>
-      <c r="Q65" s="128"/>
-      <c r="R65" s="128"/>
-      <c r="S65" s="128"/>
-      <c r="T65" s="128"/>
-      <c r="U65" s="128"/>
-      <c r="V65" s="128"/>
-      <c r="W65" s="149"/>
-      <c r="X65" s="150" t="s">
+      <c r="Q65" s="122"/>
+      <c r="R65" s="122"/>
+      <c r="S65" s="122"/>
+      <c r="T65" s="122"/>
+      <c r="U65" s="122"/>
+      <c r="V65" s="122"/>
+      <c r="W65" s="123"/>
+      <c r="X65" s="124" t="s">
         <v>83</v>
       </c>
-      <c r="Y65" s="128"/>
-      <c r="Z65" s="129"/>
+      <c r="Y65" s="122"/>
+      <c r="Z65" s="125"/>
     </row>
     <row r="66" spans="1:26" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A66" s="26" t="s">
@@ -6663,333 +6658,540 @@
       <c r="B66" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="C66" s="151" t="s">
+      <c r="C66" s="126" t="s">
         <v>107</v>
       </c>
-      <c r="D66" s="152"/>
-      <c r="E66" s="153"/>
-      <c r="F66" s="154" t="s">
+      <c r="D66" s="127"/>
+      <c r="E66" s="128"/>
+      <c r="F66" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="G66" s="155"/>
+      <c r="G66" s="129"/>
       <c r="H66" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="I66" s="156" t="s">
+      <c r="I66" s="130" t="s">
         <v>108</v>
       </c>
-      <c r="J66" s="157"/>
-      <c r="K66" s="157"/>
-      <c r="L66" s="157"/>
-      <c r="M66" s="157"/>
-      <c r="N66" s="157"/>
-      <c r="O66" s="158"/>
-      <c r="P66" s="159"/>
-      <c r="Q66" s="160"/>
-      <c r="R66" s="160"/>
-      <c r="S66" s="160"/>
-      <c r="T66" s="160"/>
-      <c r="U66" s="160"/>
-      <c r="V66" s="160"/>
-      <c r="W66" s="161"/>
-      <c r="X66" s="162"/>
-      <c r="Y66" s="160"/>
-      <c r="Z66" s="163"/>
+      <c r="J66" s="131"/>
+      <c r="K66" s="131"/>
+      <c r="L66" s="131"/>
+      <c r="M66" s="131"/>
+      <c r="N66" s="131"/>
+      <c r="O66" s="132"/>
+      <c r="P66" s="133"/>
+      <c r="Q66" s="134"/>
+      <c r="R66" s="134"/>
+      <c r="S66" s="134"/>
+      <c r="T66" s="134"/>
+      <c r="U66" s="134"/>
+      <c r="V66" s="134"/>
+      <c r="W66" s="135"/>
+      <c r="X66" s="136"/>
+      <c r="Y66" s="134"/>
+      <c r="Z66" s="137"/>
     </row>
     <row r="67" spans="1:26" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="133" t="s">
+      <c r="A67" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="B67" s="122"/>
-      <c r="C67" s="122"/>
-      <c r="D67" s="122"/>
-      <c r="E67" s="123"/>
-      <c r="F67" s="189">
+      <c r="B67" s="90"/>
+      <c r="C67" s="90"/>
+      <c r="D67" s="90"/>
+      <c r="E67" s="91"/>
+      <c r="F67" s="101">
         <v>0</v>
       </c>
-      <c r="G67" s="190"/>
-      <c r="H67" s="190"/>
-      <c r="I67" s="190"/>
-      <c r="J67" s="190"/>
-      <c r="K67" s="190"/>
-      <c r="L67" s="190"/>
-      <c r="M67" s="190"/>
-      <c r="N67" s="190"/>
-      <c r="O67" s="190"/>
-      <c r="P67" s="190"/>
-      <c r="Q67" s="190"/>
-      <c r="R67" s="190"/>
-      <c r="S67" s="190"/>
-      <c r="T67" s="190"/>
-      <c r="U67" s="190"/>
-      <c r="V67" s="190"/>
-      <c r="W67" s="190"/>
-      <c r="X67" s="190"/>
-      <c r="Y67" s="190"/>
-      <c r="Z67" s="191"/>
-    </row>
-    <row r="68" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="181" t="s">
+      <c r="G67" s="102"/>
+      <c r="H67" s="102"/>
+      <c r="I67" s="102"/>
+      <c r="J67" s="102"/>
+      <c r="K67" s="102"/>
+      <c r="L67" s="102"/>
+      <c r="M67" s="102"/>
+      <c r="N67" s="102"/>
+      <c r="O67" s="102"/>
+      <c r="P67" s="102"/>
+      <c r="Q67" s="102"/>
+      <c r="R67" s="102"/>
+      <c r="S67" s="102"/>
+      <c r="T67" s="102"/>
+      <c r="U67" s="102"/>
+      <c r="V67" s="102"/>
+      <c r="W67" s="102"/>
+      <c r="X67" s="102"/>
+      <c r="Y67" s="102"/>
+      <c r="Z67" s="103"/>
+    </row>
+    <row r="68" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="92" t="s">
         <v>69</v>
       </c>
-      <c r="B68" s="182"/>
-      <c r="C68" s="182"/>
-      <c r="D68" s="182"/>
-      <c r="E68" s="183"/>
-      <c r="F68" s="134" t="s">
+      <c r="B68" s="93"/>
+      <c r="C68" s="93"/>
+      <c r="D68" s="93"/>
+      <c r="E68" s="94"/>
+      <c r="F68" s="104" t="s">
         <v>74</v>
       </c>
-      <c r="G68" s="192"/>
-      <c r="H68" s="197" t="s">
+      <c r="G68" s="105"/>
+      <c r="H68" s="110" t="s">
         <v>84</v>
       </c>
-      <c r="I68" s="198"/>
-      <c r="J68" s="198"/>
-      <c r="K68" s="198"/>
-      <c r="L68" s="198"/>
-      <c r="M68" s="198"/>
-      <c r="N68" s="198"/>
-      <c r="O68" s="199"/>
-      <c r="P68" s="192" t="s">
+      <c r="I68" s="111"/>
+      <c r="J68" s="111"/>
+      <c r="K68" s="111"/>
+      <c r="L68" s="111"/>
+      <c r="M68" s="111"/>
+      <c r="N68" s="111"/>
+      <c r="O68" s="112"/>
+      <c r="P68" s="105" t="s">
         <v>85</v>
       </c>
-      <c r="Q68" s="192"/>
-      <c r="R68" s="192"/>
-      <c r="S68" s="192"/>
-      <c r="T68" s="192"/>
-      <c r="U68" s="192"/>
-      <c r="V68" s="192"/>
-      <c r="W68" s="192"/>
-      <c r="X68" s="192"/>
-      <c r="Y68" s="192"/>
-      <c r="Z68" s="200"/>
-    </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A69" s="181" t="s">
+      <c r="Q68" s="105"/>
+      <c r="R68" s="105"/>
+      <c r="S68" s="105"/>
+      <c r="T68" s="105"/>
+      <c r="U68" s="105"/>
+      <c r="V68" s="105"/>
+      <c r="W68" s="105"/>
+      <c r="X68" s="105"/>
+      <c r="Y68" s="105"/>
+      <c r="Z68" s="113"/>
+    </row>
+    <row r="69" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="B69" s="182"/>
-      <c r="C69" s="182"/>
-      <c r="D69" s="182"/>
-      <c r="E69" s="183"/>
-      <c r="F69" s="193"/>
-      <c r="G69" s="194"/>
-      <c r="H69" s="133" t="s">
+      <c r="B69" s="93"/>
+      <c r="C69" s="93"/>
+      <c r="D69" s="93"/>
+      <c r="E69" s="94"/>
+      <c r="F69" s="106"/>
+      <c r="G69" s="107"/>
+      <c r="H69" s="89" t="s">
         <v>71</v>
       </c>
-      <c r="I69" s="122"/>
-      <c r="J69" s="122"/>
-      <c r="K69" s="122"/>
-      <c r="L69" s="122"/>
-      <c r="M69" s="122"/>
-      <c r="N69" s="122"/>
-      <c r="O69" s="123"/>
-      <c r="P69" s="194"/>
-      <c r="Q69" s="194"/>
-      <c r="R69" s="194"/>
-      <c r="S69" s="194"/>
-      <c r="T69" s="194"/>
-      <c r="U69" s="194"/>
-      <c r="V69" s="194"/>
-      <c r="W69" s="194"/>
-      <c r="X69" s="194"/>
-      <c r="Y69" s="194"/>
-      <c r="Z69" s="201"/>
-    </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A70" s="181" t="s">
+      <c r="I69" s="90"/>
+      <c r="J69" s="90"/>
+      <c r="K69" s="90"/>
+      <c r="L69" s="90"/>
+      <c r="M69" s="90"/>
+      <c r="N69" s="90"/>
+      <c r="O69" s="91"/>
+      <c r="P69" s="107"/>
+      <c r="Q69" s="107"/>
+      <c r="R69" s="107"/>
+      <c r="S69" s="107"/>
+      <c r="T69" s="107"/>
+      <c r="U69" s="107"/>
+      <c r="V69" s="107"/>
+      <c r="W69" s="107"/>
+      <c r="X69" s="107"/>
+      <c r="Y69" s="107"/>
+      <c r="Z69" s="114"/>
+    </row>
+    <row r="70" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="B70" s="182"/>
-      <c r="C70" s="182"/>
-      <c r="D70" s="182"/>
-      <c r="E70" s="183"/>
-      <c r="F70" s="193"/>
-      <c r="G70" s="194"/>
-      <c r="H70" s="133"/>
-      <c r="I70" s="122"/>
-      <c r="J70" s="122"/>
-      <c r="K70" s="122"/>
-      <c r="L70" s="122"/>
-      <c r="M70" s="122"/>
-      <c r="N70" s="122"/>
-      <c r="O70" s="123"/>
-      <c r="P70" s="194"/>
-      <c r="Q70" s="194"/>
-      <c r="R70" s="194"/>
-      <c r="S70" s="194"/>
-      <c r="T70" s="194"/>
-      <c r="U70" s="194"/>
-      <c r="V70" s="194"/>
-      <c r="W70" s="194"/>
-      <c r="X70" s="194"/>
-      <c r="Y70" s="194"/>
-      <c r="Z70" s="201"/>
-    </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A71" s="178"/>
-      <c r="B71" s="179"/>
-      <c r="C71" s="179"/>
-      <c r="D71" s="179"/>
-      <c r="E71" s="180"/>
-      <c r="F71" s="193"/>
-      <c r="G71" s="194"/>
-      <c r="H71" s="133" t="s">
+      <c r="B70" s="93"/>
+      <c r="C70" s="93"/>
+      <c r="D70" s="93"/>
+      <c r="E70" s="94"/>
+      <c r="F70" s="106"/>
+      <c r="G70" s="107"/>
+      <c r="H70" s="89"/>
+      <c r="I70" s="90"/>
+      <c r="J70" s="90"/>
+      <c r="K70" s="90"/>
+      <c r="L70" s="90"/>
+      <c r="M70" s="90"/>
+      <c r="N70" s="90"/>
+      <c r="O70" s="91"/>
+      <c r="P70" s="107"/>
+      <c r="Q70" s="107"/>
+      <c r="R70" s="107"/>
+      <c r="S70" s="107"/>
+      <c r="T70" s="107"/>
+      <c r="U70" s="107"/>
+      <c r="V70" s="107"/>
+      <c r="W70" s="107"/>
+      <c r="X70" s="107"/>
+      <c r="Y70" s="107"/>
+      <c r="Z70" s="114"/>
+    </row>
+    <row r="71" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="86"/>
+      <c r="B71" s="87"/>
+      <c r="C71" s="87"/>
+      <c r="D71" s="87"/>
+      <c r="E71" s="88"/>
+      <c r="F71" s="106"/>
+      <c r="G71" s="107"/>
+      <c r="H71" s="89" t="s">
         <v>72</v>
       </c>
-      <c r="I71" s="122"/>
-      <c r="J71" s="122"/>
-      <c r="K71" s="122"/>
-      <c r="L71" s="122"/>
-      <c r="M71" s="122"/>
-      <c r="N71" s="122"/>
-      <c r="O71" s="123"/>
-      <c r="P71" s="194"/>
-      <c r="Q71" s="194"/>
-      <c r="R71" s="194"/>
-      <c r="S71" s="194"/>
-      <c r="T71" s="194"/>
-      <c r="U71" s="194"/>
-      <c r="V71" s="194"/>
-      <c r="W71" s="194"/>
-      <c r="X71" s="194"/>
-      <c r="Y71" s="194"/>
-      <c r="Z71" s="201"/>
-    </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A72" s="181" t="s">
+      <c r="I71" s="90"/>
+      <c r="J71" s="90"/>
+      <c r="K71" s="90"/>
+      <c r="L71" s="90"/>
+      <c r="M71" s="90"/>
+      <c r="N71" s="90"/>
+      <c r="O71" s="91"/>
+      <c r="P71" s="107"/>
+      <c r="Q71" s="107"/>
+      <c r="R71" s="107"/>
+      <c r="S71" s="107"/>
+      <c r="T71" s="107"/>
+      <c r="U71" s="107"/>
+      <c r="V71" s="107"/>
+      <c r="W71" s="107"/>
+      <c r="X71" s="107"/>
+      <c r="Y71" s="107"/>
+      <c r="Z71" s="114"/>
+    </row>
+    <row r="72" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="B72" s="182"/>
-      <c r="C72" s="182"/>
-      <c r="D72" s="182"/>
-      <c r="E72" s="183"/>
-      <c r="F72" s="193"/>
-      <c r="G72" s="194"/>
-      <c r="H72" s="133"/>
-      <c r="I72" s="122"/>
-      <c r="J72" s="122"/>
-      <c r="K72" s="122"/>
-      <c r="L72" s="122"/>
-      <c r="M72" s="122"/>
-      <c r="N72" s="122"/>
-      <c r="O72" s="123"/>
-      <c r="P72" s="194"/>
-      <c r="Q72" s="194"/>
-      <c r="R72" s="194"/>
-      <c r="S72" s="194"/>
-      <c r="T72" s="194"/>
-      <c r="U72" s="194"/>
-      <c r="V72" s="194"/>
-      <c r="W72" s="194"/>
-      <c r="X72" s="194"/>
-      <c r="Y72" s="194"/>
-      <c r="Z72" s="201"/>
-    </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A73" s="184"/>
-      <c r="B73" s="60"/>
-      <c r="C73" s="60"/>
-      <c r="D73" s="60"/>
-      <c r="E73" s="185"/>
-      <c r="F73" s="193"/>
-      <c r="G73" s="194"/>
-      <c r="H73" s="186" t="s">
+      <c r="B72" s="93"/>
+      <c r="C72" s="93"/>
+      <c r="D72" s="93"/>
+      <c r="E72" s="94"/>
+      <c r="F72" s="106"/>
+      <c r="G72" s="107"/>
+      <c r="H72" s="89"/>
+      <c r="I72" s="90"/>
+      <c r="J72" s="90"/>
+      <c r="K72" s="90"/>
+      <c r="L72" s="90"/>
+      <c r="M72" s="90"/>
+      <c r="N72" s="90"/>
+      <c r="O72" s="91"/>
+      <c r="P72" s="107"/>
+      <c r="Q72" s="107"/>
+      <c r="R72" s="107"/>
+      <c r="S72" s="107"/>
+      <c r="T72" s="107"/>
+      <c r="U72" s="107"/>
+      <c r="V72" s="107"/>
+      <c r="W72" s="107"/>
+      <c r="X72" s="107"/>
+      <c r="Y72" s="107"/>
+      <c r="Z72" s="114"/>
+    </row>
+    <row r="73" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="95"/>
+      <c r="B73" s="96"/>
+      <c r="C73" s="96"/>
+      <c r="D73" s="96"/>
+      <c r="E73" s="97"/>
+      <c r="F73" s="106"/>
+      <c r="G73" s="107"/>
+      <c r="H73" s="98" t="s">
         <v>73</v>
       </c>
-      <c r="I73" s="187"/>
-      <c r="J73" s="187"/>
-      <c r="K73" s="187"/>
-      <c r="L73" s="187"/>
-      <c r="M73" s="187"/>
-      <c r="N73" s="187"/>
-      <c r="O73" s="188"/>
-      <c r="P73" s="194"/>
-      <c r="Q73" s="194"/>
-      <c r="R73" s="194"/>
-      <c r="S73" s="194"/>
-      <c r="T73" s="194"/>
-      <c r="U73" s="194"/>
-      <c r="V73" s="194"/>
-      <c r="W73" s="194"/>
-      <c r="X73" s="194"/>
-      <c r="Y73" s="194"/>
-      <c r="Z73" s="201"/>
-    </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A74" s="166" t="s">
+      <c r="I73" s="99"/>
+      <c r="J73" s="99"/>
+      <c r="K73" s="99"/>
+      <c r="L73" s="99"/>
+      <c r="M73" s="99"/>
+      <c r="N73" s="99"/>
+      <c r="O73" s="100"/>
+      <c r="P73" s="107"/>
+      <c r="Q73" s="107"/>
+      <c r="R73" s="107"/>
+      <c r="S73" s="107"/>
+      <c r="T73" s="107"/>
+      <c r="U73" s="107"/>
+      <c r="V73" s="107"/>
+      <c r="W73" s="107"/>
+      <c r="X73" s="107"/>
+      <c r="Y73" s="107"/>
+      <c r="Z73" s="114"/>
+    </row>
+    <row r="74" spans="1:26" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="B74" s="167"/>
-      <c r="C74" s="167"/>
-      <c r="D74" s="167"/>
-      <c r="E74" s="168"/>
-      <c r="F74" s="193"/>
-      <c r="G74" s="194"/>
-      <c r="H74" s="169"/>
-      <c r="I74" s="170"/>
-      <c r="J74" s="170"/>
-      <c r="K74" s="170"/>
-      <c r="L74" s="170"/>
-      <c r="M74" s="170"/>
-      <c r="N74" s="170"/>
-      <c r="O74" s="171"/>
-      <c r="P74" s="194"/>
-      <c r="Q74" s="194"/>
-      <c r="R74" s="194"/>
-      <c r="S74" s="194"/>
-      <c r="T74" s="194"/>
-      <c r="U74" s="194"/>
-      <c r="V74" s="194"/>
-      <c r="W74" s="194"/>
-      <c r="X74" s="194"/>
-      <c r="Y74" s="194"/>
-      <c r="Z74" s="201"/>
-    </row>
-    <row r="75" spans="1:26" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="172"/>
-      <c r="B75" s="173"/>
-      <c r="C75" s="173"/>
-      <c r="D75" s="173"/>
-      <c r="E75" s="174"/>
-      <c r="F75" s="195"/>
-      <c r="G75" s="196"/>
-      <c r="H75" s="175"/>
-      <c r="I75" s="176"/>
-      <c r="J75" s="176"/>
-      <c r="K75" s="176"/>
-      <c r="L75" s="176"/>
-      <c r="M75" s="176"/>
-      <c r="N75" s="176"/>
-      <c r="O75" s="177"/>
-      <c r="P75" s="196"/>
-      <c r="Q75" s="196"/>
-      <c r="R75" s="196"/>
-      <c r="S75" s="196"/>
-      <c r="T75" s="196"/>
-      <c r="U75" s="196"/>
-      <c r="V75" s="196"/>
-      <c r="W75" s="196"/>
-      <c r="X75" s="196"/>
-      <c r="Y75" s="196"/>
-      <c r="Z75" s="202"/>
+      <c r="B74" s="73"/>
+      <c r="C74" s="73"/>
+      <c r="D74" s="73"/>
+      <c r="E74" s="74"/>
+      <c r="F74" s="106"/>
+      <c r="G74" s="107"/>
+      <c r="H74" s="75"/>
+      <c r="I74" s="76"/>
+      <c r="J74" s="76"/>
+      <c r="K74" s="76"/>
+      <c r="L74" s="76"/>
+      <c r="M74" s="76"/>
+      <c r="N74" s="76"/>
+      <c r="O74" s="77"/>
+      <c r="P74" s="107"/>
+      <c r="Q74" s="107"/>
+      <c r="R74" s="107"/>
+      <c r="S74" s="107"/>
+      <c r="T74" s="107"/>
+      <c r="U74" s="107"/>
+      <c r="V74" s="107"/>
+      <c r="W74" s="107"/>
+      <c r="X74" s="107"/>
+      <c r="Y74" s="107"/>
+      <c r="Z74" s="114"/>
+    </row>
+    <row r="75" spans="1:26" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="78"/>
+      <c r="B75" s="79"/>
+      <c r="C75" s="79"/>
+      <c r="D75" s="79"/>
+      <c r="E75" s="80"/>
+      <c r="F75" s="108"/>
+      <c r="G75" s="109"/>
+      <c r="H75" s="81"/>
+      <c r="I75" s="82"/>
+      <c r="J75" s="82"/>
+      <c r="K75" s="82"/>
+      <c r="L75" s="82"/>
+      <c r="M75" s="82"/>
+      <c r="N75" s="82"/>
+      <c r="O75" s="83"/>
+      <c r="P75" s="109"/>
+      <c r="Q75" s="109"/>
+      <c r="R75" s="109"/>
+      <c r="S75" s="109"/>
+      <c r="T75" s="109"/>
+      <c r="U75" s="109"/>
+      <c r="V75" s="109"/>
+      <c r="W75" s="109"/>
+      <c r="X75" s="109"/>
+      <c r="Y75" s="109"/>
+      <c r="Z75" s="115"/>
     </row>
   </sheetData>
   <mergeCells count="259">
-    <mergeCell ref="W50:Z50"/>
-    <mergeCell ref="W51:Z51"/>
-    <mergeCell ref="W52:Z52"/>
-    <mergeCell ref="W53:Z53"/>
-    <mergeCell ref="W54:Z54"/>
-    <mergeCell ref="W55:Z55"/>
-    <mergeCell ref="W12:Z15"/>
-    <mergeCell ref="W16:Z16"/>
-    <mergeCell ref="W17:Z17"/>
-    <mergeCell ref="W18:Z18"/>
-    <mergeCell ref="W19:Z19"/>
-    <mergeCell ref="W20:Z20"/>
-    <mergeCell ref="W48:Z48"/>
-    <mergeCell ref="W49:Z49"/>
+    <mergeCell ref="N1:Y1"/>
+    <mergeCell ref="A2:H5"/>
+    <mergeCell ref="N2:Y2"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="M3:Z3"/>
+    <mergeCell ref="I4:M4"/>
+    <mergeCell ref="W4:Y4"/>
+    <mergeCell ref="N4:V4"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:X7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:Q8"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="U8:Z8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="I10:M10"/>
+    <mergeCell ref="N10:Z10"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="N11:Z11"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:M9"/>
+    <mergeCell ref="N9:U9"/>
+    <mergeCell ref="V9:Z9"/>
+    <mergeCell ref="J12:J15"/>
+    <mergeCell ref="K12:M13"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B12:C15"/>
+    <mergeCell ref="D12:E15"/>
+    <mergeCell ref="F12:G15"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="I12:I15"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="W22:Z22"/>
+    <mergeCell ref="W23:Z23"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="W21:Z21"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="W26:Z26"/>
+    <mergeCell ref="W27:Z27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="W24:Z24"/>
+    <mergeCell ref="W25:Z25"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="W30:Z30"/>
+    <mergeCell ref="W31:Z31"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="W28:Z28"/>
+    <mergeCell ref="W29:Z29"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="W34:Z34"/>
+    <mergeCell ref="W35:Z35"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="W32:Z32"/>
+    <mergeCell ref="W33:Z33"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="W38:Z38"/>
+    <mergeCell ref="W39:Z39"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="W36:Z36"/>
+    <mergeCell ref="W37:Z37"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="W42:Z42"/>
+    <mergeCell ref="W43:Z43"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="W40:Z40"/>
+    <mergeCell ref="W41:Z41"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="W46:Z46"/>
+    <mergeCell ref="W47:Z47"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="W44:Z44"/>
+    <mergeCell ref="W45:Z45"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="A51:E55"/>
+    <mergeCell ref="F51:M51"/>
+    <mergeCell ref="F52:M52"/>
+    <mergeCell ref="F53:M53"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="P57:Z57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="I58:O58"/>
+    <mergeCell ref="P58:Z58"/>
+    <mergeCell ref="F54:M54"/>
+    <mergeCell ref="F55:M55"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="F56:G57"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="I56:O57"/>
+    <mergeCell ref="P56:Z56"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="I61:O61"/>
+    <mergeCell ref="P61:Z61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="I62:O62"/>
+    <mergeCell ref="P62:Z62"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="I59:O59"/>
+    <mergeCell ref="P59:Z59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="I60:O60"/>
+    <mergeCell ref="P60:Z60"/>
+    <mergeCell ref="I65:O65"/>
+    <mergeCell ref="P65:W65"/>
+    <mergeCell ref="X65:Z65"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="I66:O66"/>
+    <mergeCell ref="P66:W66"/>
+    <mergeCell ref="X66:Z66"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="I63:O63"/>
+    <mergeCell ref="P63:Z63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="I64:O64"/>
+    <mergeCell ref="P64:Z64"/>
     <mergeCell ref="A74:E74"/>
     <mergeCell ref="H74:O74"/>
     <mergeCell ref="A75:E75"/>
@@ -7014,229 +7216,22 @@
     <mergeCell ref="H70:O70"/>
     <mergeCell ref="C65:E65"/>
     <mergeCell ref="F65:G65"/>
-    <mergeCell ref="I65:O65"/>
-    <mergeCell ref="P65:W65"/>
-    <mergeCell ref="X65:Z65"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="I66:O66"/>
-    <mergeCell ref="P66:W66"/>
-    <mergeCell ref="X66:Z66"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="I63:O63"/>
-    <mergeCell ref="P63:Z63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="I64:O64"/>
-    <mergeCell ref="P64:Z64"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="I61:O61"/>
-    <mergeCell ref="P61:Z61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="I62:O62"/>
-    <mergeCell ref="P62:Z62"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="I59:O59"/>
-    <mergeCell ref="P59:Z59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="I60:O60"/>
-    <mergeCell ref="P60:Z60"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="P57:Z57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="I58:O58"/>
-    <mergeCell ref="P58:Z58"/>
-    <mergeCell ref="F54:M54"/>
-    <mergeCell ref="F55:M55"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="F56:G57"/>
-    <mergeCell ref="H56:H57"/>
-    <mergeCell ref="I56:O57"/>
-    <mergeCell ref="P56:Z56"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="A51:E55"/>
-    <mergeCell ref="F51:M51"/>
-    <mergeCell ref="F52:M52"/>
-    <mergeCell ref="F53:M53"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="W46:Z46"/>
-    <mergeCell ref="W47:Z47"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="W44:Z44"/>
-    <mergeCell ref="W45:Z45"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="W42:Z42"/>
-    <mergeCell ref="W43:Z43"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="W40:Z40"/>
-    <mergeCell ref="W41:Z41"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="W38:Z38"/>
-    <mergeCell ref="W39:Z39"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="W36:Z36"/>
-    <mergeCell ref="W37:Z37"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="W34:Z34"/>
-    <mergeCell ref="W35:Z35"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="W32:Z32"/>
-    <mergeCell ref="W33:Z33"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="W30:Z30"/>
-    <mergeCell ref="W31:Z31"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="W28:Z28"/>
-    <mergeCell ref="W29:Z29"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="W26:Z26"/>
-    <mergeCell ref="W27:Z27"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="W24:Z24"/>
-    <mergeCell ref="W25:Z25"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="W22:Z22"/>
-    <mergeCell ref="W23:Z23"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="W21:Z21"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="N11:Z11"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:M9"/>
-    <mergeCell ref="N9:U9"/>
-    <mergeCell ref="V9:Z9"/>
-    <mergeCell ref="J12:J15"/>
-    <mergeCell ref="K12:M13"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="B12:C15"/>
-    <mergeCell ref="D12:E15"/>
-    <mergeCell ref="F12:G15"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="I12:I15"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:X7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:Q8"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="U8:Z8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="I10:M10"/>
-    <mergeCell ref="N10:Z10"/>
-    <mergeCell ref="N1:Y1"/>
-    <mergeCell ref="A2:H5"/>
-    <mergeCell ref="N2:Y2"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="M3:Z3"/>
-    <mergeCell ref="I4:M4"/>
-    <mergeCell ref="W4:Y4"/>
-    <mergeCell ref="N4:V4"/>
-    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="W50:Z50"/>
+    <mergeCell ref="W51:Z51"/>
+    <mergeCell ref="W52:Z52"/>
+    <mergeCell ref="W53:Z53"/>
+    <mergeCell ref="W54:Z54"/>
+    <mergeCell ref="W55:Z55"/>
+    <mergeCell ref="W12:Z15"/>
+    <mergeCell ref="W16:Z16"/>
+    <mergeCell ref="W17:Z17"/>
+    <mergeCell ref="W18:Z18"/>
+    <mergeCell ref="W19:Z19"/>
+    <mergeCell ref="W20:Z20"/>
+    <mergeCell ref="W48:Z48"/>
+    <mergeCell ref="W49:Z49"/>
   </mergeCells>
-  <pageMargins left="0.1" right="0" top="0.1" bottom="0" header="0" footer="0"/>
+  <pageMargins left="0.1" right="0.02" top="0.1" bottom="0" header="0" footer="0"/>
   <pageSetup paperSize="14" scale="74" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
